--- a/Ostalo/kalkulacije.xlsx
+++ b/Ostalo/kalkulacije.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\KalkulacijeGradjevina\Ostalo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HT-ICT\Documents\GitHub\KalkulacijeGradjevina\Ostalo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3F07BC-294A-4E45-A2F9-87F259D5828C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1A899C27-4981-4013-83D0-612D28855781}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Bušenje" sheetId="1" r:id="rId1"/>
     <sheet name="Rezanje stropa" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -211,17 +210,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="7">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;kn&quot;_-;\-* #,##0.00\ &quot;kn&quot;_-;_-* &quot;-&quot;??\ &quot;kn&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.00\ [$€-41A]_-;\-* #,##0.00\ [$€-41A]_-;_-* &quot;-&quot;??\ [$€-41A]_-;_-@_-"/>
-    <numFmt numFmtId="174" formatCode="#,##0\ [$€-1];[Red]\-#,##0\ [$€-1]"/>
-    <numFmt numFmtId="176" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ [$€-41A]_-;\-* #,##0.00\ [$€-41A]_-;_-* &quot;-&quot;??\ [$€-41A]_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="#,##0\ [$€-1];[Red]\-#,##0\ [$€-1]"/>
+    <numFmt numFmtId="168" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,6 +256,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -312,19 +318,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -332,23 +338,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Normalno" xfId="0" builtinId="0"/>
-    <cellStyle name="Postotak" xfId="1" builtinId="5"/>
-    <cellStyle name="Valuta" xfId="3" builtinId="4"/>
-    <cellStyle name="Zarez" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -659,24 +667,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5676D419-5947-4DD5-A3DD-6DE0C11E4084}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" customWidth="1"/>
+    <col min="1" max="1" width="5.26953125" customWidth="1"/>
+    <col min="2" max="2" width="22.54296875" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.42578125" customWidth="1"/>
-    <col min="12" max="12" width="22.85546875" customWidth="1"/>
-    <col min="17" max="17" width="22.28515625" customWidth="1"/>
+    <col min="7" max="7" width="22.453125" customWidth="1"/>
+    <col min="12" max="12" width="22.81640625" customWidth="1"/>
+    <col min="17" max="17" width="22.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -718,7 +726,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
@@ -763,7 +771,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
@@ -808,7 +816,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
@@ -853,7 +861,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B9" s="5" t="s">
         <v>21</v>
       </c>
@@ -898,7 +906,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B10" s="5" t="s">
         <v>25</v>
       </c>
@@ -943,7 +951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B11" s="5" t="s">
         <v>1</v>
       </c>
@@ -988,7 +996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C12" s="6" t="s">
         <v>26</v>
       </c>
@@ -1021,9 +1029,9 @@
         <v>102.12</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B15" t="str">
-        <f>B6</f>
+        <f t="shared" ref="B15:B20" si="3">B6</f>
         <v>promjer rupe mm</v>
       </c>
       <c r="C15">
@@ -1034,7 +1042,7 @@
         <v>6.2</v>
       </c>
       <c r="G15" t="str">
-        <f t="shared" ref="G15:G20" si="3">B15</f>
+        <f t="shared" ref="G15:G20" si="4">B15</f>
         <v>promjer rupe mm</v>
       </c>
       <c r="H15">
@@ -1045,7 +1053,7 @@
         <v>25</v>
       </c>
       <c r="L15" t="str">
-        <f t="shared" ref="L15:L20" si="4">G15</f>
+        <f t="shared" ref="L15:L20" si="5">G15</f>
         <v>promjer rupe mm</v>
       </c>
       <c r="M15">
@@ -1056,7 +1064,7 @@
         <v>5.2</v>
       </c>
       <c r="Q15" t="str">
-        <f t="shared" ref="Q15:Q20" si="5">L15</f>
+        <f t="shared" ref="Q15:Q20" si="6">L15</f>
         <v>promjer rupe mm</v>
       </c>
       <c r="R15">
@@ -1067,9 +1075,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B16" t="str">
-        <f>B7</f>
+        <f t="shared" si="3"/>
         <v>vrsta bušenja</v>
       </c>
       <c r="C16">
@@ -1080,7 +1088,7 @@
         <v>0.17</v>
       </c>
       <c r="G16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>vrsta bušenja</v>
       </c>
       <c r="H16">
@@ -1091,7 +1099,7 @@
         <v>0.08</v>
       </c>
       <c r="L16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>vrsta bušenja</v>
       </c>
       <c r="M16">
@@ -1102,7 +1110,7 @@
         <v>0.3</v>
       </c>
       <c r="Q16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>vrsta bušenja</v>
       </c>
       <c r="R16">
@@ -1113,9 +1121,9 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B17" t="str">
-        <f>B8</f>
+        <f t="shared" si="3"/>
         <v>dubina ukupna cm</v>
       </c>
       <c r="C17">
@@ -1126,7 +1134,7 @@
         <v>25</v>
       </c>
       <c r="G17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>dubina ukupna cm</v>
       </c>
       <c r="H17">
@@ -1137,7 +1145,7 @@
         <v>105</v>
       </c>
       <c r="L17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>dubina ukupna cm</v>
       </c>
       <c r="M17">
@@ -1148,7 +1156,7 @@
         <v>20</v>
       </c>
       <c r="Q17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>dubina ukupna cm</v>
       </c>
       <c r="R17">
@@ -1159,9 +1167,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B18" t="str">
-        <f>B9</f>
+        <f t="shared" si="3"/>
         <v>zaštita (0-NE; 1-DA)</v>
       </c>
       <c r="C18">
@@ -1205,9 +1213,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B19" t="str">
-        <f>B10</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">ankerisanje </v>
       </c>
       <c r="C19">
@@ -1218,7 +1226,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">ankerisanje </v>
       </c>
       <c r="H19">
@@ -1229,7 +1237,7 @@
         <v>20</v>
       </c>
       <c r="L19" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">ankerisanje </v>
       </c>
       <c r="M19">
@@ -1240,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">ankerisanje </v>
       </c>
       <c r="R19">
@@ -1251,9 +1259,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B20" t="str">
-        <f>B11</f>
+        <f t="shared" si="3"/>
         <v>broj rupa</v>
       </c>
       <c r="C20">
@@ -1264,7 +1272,7 @@
         <v>1</v>
       </c>
       <c r="G20" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>broj rupa</v>
       </c>
       <c r="H20">
@@ -1275,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="L20" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>broj rupa</v>
       </c>
       <c r="M20">
@@ -1286,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>broj rupa</v>
       </c>
       <c r="R20">
@@ -1297,7 +1305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C21" t="str">
         <f>C12</f>
         <v>Ukupno:</v>
@@ -1331,7 +1339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B24" t="str">
         <f>B15</f>
         <v>promjer rupe mm</v>
@@ -1344,7 +1352,7 @@
         <v>11</v>
       </c>
       <c r="G24" t="str">
-        <f t="shared" ref="G24:G29" si="6">B24</f>
+        <f t="shared" ref="G24:G29" si="7">B24</f>
         <v>promjer rupe mm</v>
       </c>
       <c r="H24">
@@ -1355,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="str">
-        <f t="shared" ref="L24:L30" si="7">G24</f>
+        <f t="shared" ref="L24:L29" si="8">G24</f>
         <v>promjer rupe mm</v>
       </c>
       <c r="M24">
@@ -1366,7 +1374,7 @@
         <v>5.2</v>
       </c>
       <c r="Q24" t="str">
-        <f t="shared" ref="Q24:Q29" si="8">L24</f>
+        <f t="shared" ref="Q24:Q29" si="9">L24</f>
         <v>promjer rupe mm</v>
       </c>
       <c r="R24">
@@ -1377,7 +1385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B25" t="str">
         <f>B16</f>
         <v>vrsta bušenja</v>
@@ -1390,7 +1398,7 @@
         <v>0.17</v>
       </c>
       <c r="G25" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>vrsta bušenja</v>
       </c>
       <c r="H25">
@@ -1401,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>vrsta bušenja</v>
       </c>
       <c r="M25">
@@ -1412,7 +1420,7 @@
         <v>0.11</v>
       </c>
       <c r="Q25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>vrsta bušenja</v>
       </c>
       <c r="R25">
@@ -1423,7 +1431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B26" t="str">
         <f>B17</f>
         <v>dubina ukupna cm</v>
@@ -1436,7 +1444,7 @@
         <v>60</v>
       </c>
       <c r="G26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>dubina ukupna cm</v>
       </c>
       <c r="H26">
@@ -1447,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>dubina ukupna cm</v>
       </c>
       <c r="M26">
@@ -1458,7 +1466,7 @@
         <v>35</v>
       </c>
       <c r="Q26" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>dubina ukupna cm</v>
       </c>
       <c r="R26">
@@ -1469,7 +1477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B27" t="str">
         <f>B9</f>
         <v>zaštita (0-NE; 1-DA)</v>
@@ -1515,9 +1523,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B28" t="str">
-        <f t="shared" ref="B28:B29" si="9">B19</f>
+        <f t="shared" ref="B28:B29" si="10">B19</f>
         <v xml:space="preserve">ankerisanje </v>
       </c>
       <c r="C28">
@@ -1528,7 +1536,7 @@
         <v>10</v>
       </c>
       <c r="G28" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">ankerisanje </v>
       </c>
       <c r="H28">
@@ -1539,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">ankerisanje </v>
       </c>
       <c r="M28">
@@ -1550,7 +1558,7 @@
         <v>10</v>
       </c>
       <c r="Q28" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">ankerisanje </v>
       </c>
       <c r="R28">
@@ -1561,44 +1569,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B29" t="str">
+        <f t="shared" si="10"/>
+        <v>broj rupa</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <f>C29</f>
+        <v>0</v>
+      </c>
+      <c r="G29" t="str">
+        <f t="shared" si="7"/>
+        <v>broj rupa</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <f>H29</f>
+        <v>0</v>
+      </c>
+      <c r="L29" t="str">
+        <f t="shared" si="8"/>
+        <v>broj rupa</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <f>M29</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" t="str">
         <f t="shared" si="9"/>
         <v>broj rupa</v>
       </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29">
-        <f>C29</f>
-        <v>0</v>
-      </c>
-      <c r="G29" t="str">
-        <f t="shared" si="6"/>
-        <v>broj rupa</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <f>H29</f>
-        <v>0</v>
-      </c>
-      <c r="L29" t="str">
-        <f t="shared" si="7"/>
-        <v>broj rupa</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <f>M29</f>
-        <v>0</v>
-      </c>
-      <c r="Q29" t="str">
-        <f t="shared" si="8"/>
-        <v>broj rupa</v>
-      </c>
       <c r="R29">
         <v>0</v>
       </c>
@@ -1607,7 +1615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C30" t="str">
         <f>C21</f>
         <v>Ukupno:</v>
@@ -1645,7 +1653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>15</v>
       </c>
@@ -1678,7 +1686,7 @@
         <v>122.12</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>18</v>
       </c>
@@ -1717,7 +1725,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C34" s="3" t="s">
         <v>17</v>
       </c>
@@ -1748,7 +1756,7 @@
         <v>116.01400000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>2</v>
       </c>
@@ -1769,7 +1777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>20</v>
       </c>
@@ -1795,7 +1803,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="F40">
         <v>2</v>
       </c>
@@ -1815,7 +1823,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>0</v>
       </c>
@@ -1835,7 +1843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1</v>
       </c>
@@ -1858,7 +1866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2</v>
       </c>
@@ -1887,7 +1895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>3</v>
       </c>
@@ -1916,7 +1924,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>4</v>
       </c>
@@ -1945,10 +1953,10 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C47" s="1"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C48" s="1"/>
     </row>
   </sheetData>
@@ -1957,30 +1965,30 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BB380DE-BA90-4F1F-B831-1AD419E671FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U82"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" customWidth="1"/>
+    <col min="3" max="3" width="6.453125" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="16" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.7109375" customWidth="1"/>
+    <col min="10" max="16" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1796875" style="18" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -2006,10 +2014,10 @@
         <v>32</v>
       </c>
       <c r="P2" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="K3" s="3" t="s">
         <v>42</v>
       </c>
@@ -2017,19 +2025,19 @@
         <v>142</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="M4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="9">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -2083,11 +2091,11 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="D6" s="9">
-        <v>2.0499999999999998</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0.5</v>
@@ -2141,12 +2149,12 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="D7">
         <f>D5*D6</f>
-        <v>1.64</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f>E6*E5</f>
@@ -2217,7 +2225,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>30</v>
       </c>
@@ -2225,20 +2233,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <f>A9*$C$2/100</f>
-        <v>390</v>
+        <v>910</v>
       </c>
       <c r="D9">
         <f>D7*A9/100*C2</f>
-        <v>639.59999999999991</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+        <v>909.99999999999989</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>20</v>
       </c>
@@ -2315,7 +2323,7 @@
         <v>3250</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>25</v>
       </c>
@@ -2392,7 +2400,7 @@
         <v>4062.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>30</v>
       </c>
@@ -2469,7 +2477,7 @@
         <v>4875</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>35</v>
       </c>
@@ -2546,21 +2554,21 @@
         <v>5687.5</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A17" s="25">
         <f>A9</f>
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D17" s="9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <f>A10</f>
         <v>20</v>
@@ -2617,7 +2625,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
         <f t="shared" ref="A19:A21" si="5">A11</f>
         <v>25</v>
@@ -2674,7 +2682,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <f t="shared" si="5"/>
         <v>30</v>
@@ -2731,7 +2739,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <f t="shared" si="5"/>
         <v>35</v>
@@ -2788,7 +2796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" s="8"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
@@ -2808,7 +2816,7 @@
       <c r="T22" s="13"/>
       <c r="U22" s="13"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="D23" s="16" t="s">
         <v>44</v>
       </c>
@@ -2830,13 +2838,13 @@
       <c r="T23" s="13"/>
       <c r="U23" s="13"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="10">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A24" s="25">
         <f>A17</f>
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D24" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
@@ -2856,7 +2864,7 @@
       <c r="T24" s="13"/>
       <c r="U24" s="13"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
         <f>A18</f>
         <v>20</v>
@@ -2913,7 +2921,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <f>A19</f>
         <v>25</v>
@@ -2970,7 +2978,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
         <f>A20</f>
         <v>30</v>
@@ -3027,7 +3035,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
         <f>A21</f>
         <v>35</v>
@@ -3084,7 +3092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" s="8"/>
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
@@ -3104,7 +3112,7 @@
       <c r="T29" s="13"/>
       <c r="U29" s="13"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="D30" t="s">
         <v>47</v>
       </c>
@@ -3126,14 +3134,14 @@
       <c r="T30" s="8"/>
       <c r="U30" s="8"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="10">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A31" s="25">
         <f>A24</f>
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D31" s="12">
         <f>D9/(D17*D24)</f>
-        <v>25.583999999999996</v>
+        <v>101.1111111111111</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
@@ -3153,318 +3161,318 @@
       <c r="T31" s="8"/>
       <c r="U31" s="8"/>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
         <f>A25</f>
         <v>20</v>
       </c>
       <c r="E32" s="12">
-        <f>E10/(E18*E25)</f>
+        <f t="shared" ref="E32:F35" si="6">E10/(E18*E25)</f>
         <v>32.5</v>
       </c>
       <c r="F32" s="12">
-        <f>F10/(F18*F25)</f>
-        <v>32.5</v>
-      </c>
-      <c r="G32" s="12">
-        <f t="shared" ref="G32:U32" si="6">G10/(G18*G25)</f>
-        <v>43.333333333333336</v>
-      </c>
-      <c r="H32" s="12">
         <f t="shared" si="6"/>
         <v>32.5</v>
       </c>
+      <c r="G32" s="12">
+        <f t="shared" ref="G32:U32" si="7">G10/(G18*G25)</f>
+        <v>43.333333333333336</v>
+      </c>
+      <c r="H32" s="12">
+        <f t="shared" si="7"/>
+        <v>32.5</v>
+      </c>
       <c r="I32" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
       <c r="J32" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>40.625</v>
       </c>
       <c r="K32" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
       <c r="L32" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
       <c r="N32" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
       <c r="O32" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32.500000000000007</v>
       </c>
       <c r="P32" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32.499999999999993</v>
       </c>
       <c r="Q32" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
       <c r="R32" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
       <c r="S32" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
       <c r="T32" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
       <c r="U32" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33" s="8">
         <f>A26</f>
         <v>25</v>
       </c>
       <c r="E33" s="12">
-        <f>E11/(E19*E26)</f>
+        <f t="shared" si="6"/>
         <v>40.625</v>
       </c>
       <c r="F33" s="12">
-        <f>F11/(F19*F26)</f>
+        <f t="shared" si="6"/>
         <v>40.625</v>
       </c>
       <c r="G33" s="12">
-        <f t="shared" ref="G33:U33" si="7">G11/(G19*G26)</f>
+        <f t="shared" ref="G33:U33" si="8">G11/(G19*G26)</f>
         <v>40.625</v>
       </c>
       <c r="H33" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>40.625</v>
       </c>
       <c r="I33" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>40.625</v>
       </c>
       <c r="J33" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>40.625</v>
       </c>
       <c r="K33" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>33.854166666666664</v>
       </c>
       <c r="L33" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>33.854166666666664</v>
       </c>
       <c r="M33" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>34.821428571428569</v>
       </c>
       <c r="N33" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>40.625</v>
       </c>
       <c r="O33" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>31.103515625</v>
       </c>
       <c r="P33" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>31.597222222222221</v>
       </c>
       <c r="Q33" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>36.111111111111114</v>
       </c>
       <c r="R33" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>40.625</v>
       </c>
       <c r="S33" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>36.5625</v>
       </c>
       <c r="T33" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>36.5625</v>
       </c>
       <c r="U33" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>36.93181818181818</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A34" s="8">
         <f>A27</f>
         <v>30</v>
       </c>
       <c r="E34" s="12">
-        <f>E12/(E20*E27)</f>
+        <f t="shared" si="6"/>
         <v>32.5</v>
       </c>
       <c r="F34" s="12">
-        <f>F12/(F20*F27)</f>
+        <f t="shared" si="6"/>
         <v>36.5625</v>
       </c>
       <c r="G34" s="12">
-        <f>G12/(G20*G27)</f>
+        <f t="shared" ref="G34:T34" si="9">G12/(G20*G27)</f>
         <v>39</v>
       </c>
       <c r="H34" s="12">
-        <f>H12/(H20*H27)</f>
+        <f t="shared" si="9"/>
         <v>39</v>
       </c>
       <c r="I34" s="12">
-        <f>I12/(I20*I27)</f>
+        <f t="shared" si="9"/>
         <v>39</v>
       </c>
       <c r="J34" s="12">
-        <f>J12/(J20*J27)</f>
+        <f t="shared" si="9"/>
         <v>39</v>
       </c>
       <c r="K34" s="12">
-        <f>K12/(K20*K27)</f>
+        <f t="shared" si="9"/>
         <v>34.821428571428569</v>
       </c>
       <c r="L34" s="12">
-        <f>L12/(L20*L27)</f>
+        <f t="shared" si="9"/>
         <v>30.46875</v>
       </c>
       <c r="M34" s="12">
-        <f>M12/(M20*M27)</f>
+        <f t="shared" si="9"/>
         <v>35.816326530612251</v>
       </c>
       <c r="N34" s="12">
-        <f>N12/(N20*N27)</f>
+        <f t="shared" si="9"/>
         <v>41.785714285714285</v>
       </c>
       <c r="O34" s="12">
-        <f>O12/(O20*O27)</f>
+        <f t="shared" si="9"/>
         <v>33.177083333333336</v>
       </c>
       <c r="P34" s="12">
-        <f>P12/(P20*P27)</f>
+        <f t="shared" si="9"/>
         <v>37.916666666666664</v>
       </c>
       <c r="Q34" s="21">
-        <f>Q12/(Q20*Q27)</f>
+        <f t="shared" si="9"/>
         <v>38.518518518518519</v>
       </c>
       <c r="R34" s="12">
-        <f>R12/(R20*R27)</f>
+        <f t="shared" si="9"/>
         <v>43.333333333333336</v>
       </c>
       <c r="S34" s="12">
-        <f>S12/(S20*S27)</f>
+        <f t="shared" si="9"/>
         <v>39.487499999999997</v>
       </c>
       <c r="T34" s="12">
-        <f>T12/(T20*T27)</f>
+        <f t="shared" si="9"/>
         <v>36.260330578512395</v>
       </c>
       <c r="U34" s="12">
-        <f t="shared" ref="U34" si="8">U12/(U20*U27)</f>
+        <f t="shared" ref="U34" si="10">U12/(U20*U27)</f>
         <v>36.93181818181818</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35" s="8">
         <f>A28</f>
         <v>35</v>
       </c>
       <c r="E35" s="12">
-        <f>E13/(E21*E28)</f>
+        <f t="shared" si="6"/>
         <v>37.916666666666664</v>
       </c>
       <c r="F35" s="12">
-        <f>F13/(F21*F28)</f>
+        <f t="shared" si="6"/>
         <v>34.125</v>
       </c>
       <c r="G35" s="12">
-        <f>G13/(G21*G28)</f>
+        <f t="shared" ref="G35:T35" si="11">G13/(G21*G28)</f>
         <v>45.499999999999993</v>
       </c>
       <c r="H35" s="12">
-        <f>H13/(H21*H28)</f>
+        <f t="shared" si="11"/>
         <v>34.125</v>
       </c>
       <c r="I35" s="12">
-        <f>I13/(I21*I28)</f>
+        <f t="shared" si="11"/>
         <v>36.4</v>
       </c>
       <c r="J35" s="12">
-        <f>J13/(J21*J28)</f>
+        <f t="shared" si="11"/>
         <v>37.916666666666664</v>
       </c>
       <c r="K35" s="12">
-        <f>K13/(K21*K28)</f>
+        <f t="shared" si="11"/>
         <v>35.546875</v>
       </c>
       <c r="L35" s="12">
-        <f>L13/(L21*L28)</f>
+        <f t="shared" si="11"/>
         <v>34.821428571428569</v>
       </c>
       <c r="M35" s="12">
-        <f>M13/(M21*M28)</f>
+        <f t="shared" si="11"/>
         <v>36.5625</v>
       </c>
       <c r="N35" s="12">
-        <f>N13/(N21*N28)</f>
+        <f t="shared" si="11"/>
         <v>42.65625</v>
       </c>
       <c r="O35" s="12">
-        <f>O13/(O21*O28)</f>
+        <f t="shared" si="11"/>
         <v>34.40586419753086</v>
       </c>
       <c r="P35" s="12">
-        <f>P13/(P21*P28)</f>
+        <f t="shared" si="11"/>
         <v>35.388888888888893</v>
       </c>
       <c r="Q35" s="21">
-        <f>Q13/(Q21*Q28)</f>
+        <f t="shared" si="11"/>
         <v>36.4</v>
       </c>
       <c r="R35" s="12">
-        <f>R13/(R21*R28)</f>
+        <f t="shared" si="11"/>
         <v>40.950000000000003</v>
       </c>
       <c r="S35" s="12">
-        <f>S13/(S21*S28)</f>
+        <f t="shared" si="11"/>
         <v>41.88068181818182</v>
       </c>
       <c r="T35" s="12">
-        <f>T13/(T21*T28)</f>
+        <f t="shared" si="11"/>
         <v>38.778409090909093</v>
       </c>
       <c r="U35" s="12">
-        <f t="shared" ref="U35" si="9">U13/(U21*U28)</f>
+        <f t="shared" ref="U35" si="12">U13/(U21*U28)</f>
         <v>36.458333333333336</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="D37" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A38" s="10">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A38" s="25">
         <f>A31</f>
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D38" s="12">
         <f>(D17+1)*2+(D24-1)*2</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A39" s="8">
         <f>A32</f>
         <v>20</v>
@@ -3474,73 +3482,73 @@
         <v>8</v>
       </c>
       <c r="F39" s="12">
-        <f t="shared" ref="F39:U39" si="10">(F18+1)*2+(F25-1)*2</f>
+        <f t="shared" ref="F39:U39" si="13">(F18+1)*2+(F25-1)*2</f>
         <v>10</v>
       </c>
       <c r="G39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="H39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
       <c r="I39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>16</v>
       </c>
       <c r="J39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>16</v>
       </c>
       <c r="K39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
       <c r="L39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>22</v>
       </c>
       <c r="M39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>24</v>
       </c>
       <c r="N39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>26</v>
       </c>
       <c r="O39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>28</v>
       </c>
       <c r="P39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>30</v>
       </c>
       <c r="Q39" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>32</v>
       </c>
       <c r="R39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>34</v>
       </c>
       <c r="S39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>36</v>
       </c>
       <c r="T39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>38</v>
       </c>
       <c r="U39" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
-        <f t="shared" ref="A40:A42" si="11">A33</f>
+        <f t="shared" ref="A40:A42" si="14">A33</f>
         <v>25</v>
       </c>
       <c r="E40" s="12">
@@ -3548,73 +3556,73 @@
         <v>8</v>
       </c>
       <c r="F40" s="12">
-        <f t="shared" ref="F40:U40" si="12">(F19+1)*2+(F26-1)*2</f>
+        <f t="shared" ref="F40:U40" si="15">(F19+1)*2+(F26-1)*2</f>
         <v>10</v>
       </c>
       <c r="G40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>12</v>
       </c>
       <c r="H40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>14</v>
       </c>
       <c r="I40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>16</v>
       </c>
       <c r="J40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>18</v>
       </c>
       <c r="K40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
       <c r="L40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
       <c r="M40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>26</v>
       </c>
       <c r="N40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>26</v>
       </c>
       <c r="O40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>32</v>
       </c>
       <c r="P40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>34</v>
       </c>
       <c r="Q40" s="21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>34</v>
       </c>
       <c r="R40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>34</v>
       </c>
       <c r="S40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>38</v>
       </c>
       <c r="T40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>40</v>
       </c>
       <c r="U40" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A41" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="E41" s="12">
@@ -3622,73 +3630,73 @@
         <v>10</v>
       </c>
       <c r="F41" s="12">
-        <f t="shared" ref="F41:U41" si="13">(F20+1)*2+(F27-1)*2</f>
+        <f t="shared" ref="F41:U41" si="16">(F20+1)*2+(F27-1)*2</f>
         <v>12</v>
       </c>
       <c r="G41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="H41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>16</v>
       </c>
       <c r="I41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>18</v>
       </c>
       <c r="J41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="K41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>24</v>
       </c>
       <c r="L41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>28</v>
       </c>
       <c r="M41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>28</v>
       </c>
       <c r="N41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>28</v>
       </c>
       <c r="O41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>34</v>
       </c>
       <c r="P41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>34</v>
       </c>
       <c r="Q41" s="21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="R41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="S41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>40</v>
       </c>
       <c r="T41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>44</v>
       </c>
       <c r="U41" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A42" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>35</v>
       </c>
       <c r="E42" s="12">
@@ -3696,397 +3704,397 @@
         <v>10</v>
       </c>
       <c r="F42" s="12">
-        <f t="shared" ref="F42:U42" si="14">(F21+1)*2+(F28-1)*2</f>
+        <f t="shared" ref="F42:U42" si="17">(F21+1)*2+(F28-1)*2</f>
         <v>14</v>
       </c>
       <c r="G42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="H42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>18</v>
       </c>
       <c r="I42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>20</v>
       </c>
       <c r="J42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>22</v>
       </c>
       <c r="K42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>26</v>
       </c>
       <c r="L42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>28</v>
       </c>
       <c r="M42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>30</v>
       </c>
       <c r="N42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>30</v>
       </c>
       <c r="O42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>36</v>
       </c>
       <c r="P42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>38</v>
       </c>
       <c r="Q42" s="21">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>40</v>
       </c>
       <c r="R42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>40</v>
       </c>
       <c r="S42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>42</v>
       </c>
       <c r="T42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>46</v>
       </c>
       <c r="U42" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
       <c r="D44" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="10">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A45" s="25">
         <f>A17</f>
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D45" s="4">
-        <f>$P$2*$A$45*((D17+1)+(D24+1))</f>
-        <v>630</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+        <f>$P$2*$A$45*((D17+1)*D5+(D24+1)*D6)</f>
+        <v>840</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A46" s="8">
         <f>A39</f>
         <v>20</v>
       </c>
       <c r="E46" s="4">
-        <f>$P$2*$A$46*((E18+1)+(E25+1))</f>
-        <v>420</v>
+        <f>$P$2*$A$46*((E18+1)*E5+(E25+1)*E6)</f>
+        <v>180</v>
       </c>
       <c r="F46" s="4">
-        <f>$P$2*$A$46*((F18+1)+(F25+1))</f>
-        <v>490</v>
+        <f t="shared" ref="F46:U46" si="18">$P$2*$A$46*((F18+1)*F5+(F25+1)*F6)</f>
+        <v>270</v>
       </c>
       <c r="G46" s="4">
-        <f>$P$2*$A$46*((G18+1)+(G25+1))</f>
-        <v>490</v>
+        <f t="shared" si="18"/>
+        <v>330</v>
       </c>
       <c r="H46" s="4">
-        <f>$P$2*$A$46*((H18+1)+(H25+1))</f>
+        <f t="shared" si="18"/>
+        <v>480</v>
+      </c>
+      <c r="I46" s="4">
+        <f t="shared" si="18"/>
+        <v>600</v>
+      </c>
+      <c r="J46" s="4">
+        <f t="shared" si="18"/>
+        <v>675</v>
+      </c>
+      <c r="K46" s="4">
+        <f t="shared" si="18"/>
+        <v>900</v>
+      </c>
+      <c r="L46" s="4">
+        <f t="shared" si="18"/>
+        <v>1080</v>
+      </c>
+      <c r="M46" s="4">
+        <f t="shared" si="18"/>
+        <v>1260</v>
+      </c>
+      <c r="N46" s="4">
+        <f t="shared" si="18"/>
+        <v>1470</v>
+      </c>
+      <c r="O46" s="4">
+        <f t="shared" si="18"/>
+        <v>1680</v>
+      </c>
+      <c r="P46" s="4">
+        <f t="shared" si="18"/>
+        <v>1920</v>
+      </c>
+      <c r="Q46" s="4">
+        <f t="shared" si="18"/>
+        <v>2160</v>
+      </c>
+      <c r="R46" s="4">
+        <f t="shared" si="18"/>
+        <v>2430</v>
+      </c>
+      <c r="S46" s="4">
+        <f t="shared" si="18"/>
+        <v>2700</v>
+      </c>
+      <c r="T46" s="4">
+        <f t="shared" si="18"/>
+        <v>3000</v>
+      </c>
+      <c r="U46" s="4">
+        <f t="shared" si="18"/>
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A47" s="8">
+        <f t="shared" ref="A47:A49" si="19">A40</f>
+        <v>25</v>
+      </c>
+      <c r="E47" s="4">
+        <f>$P$2*$A$47*((E19+1)*E5+(E26+1)*E6)</f>
+        <v>225</v>
+      </c>
+      <c r="F47" s="4">
+        <f t="shared" ref="F47:U47" si="20">$P$2*$A$47*((F19+1)*F5+(F26+1)*F6)</f>
+        <v>337.5</v>
+      </c>
+      <c r="G47" s="4">
+        <f t="shared" si="20"/>
+        <v>487.5</v>
+      </c>
+      <c r="H47" s="4">
+        <f t="shared" si="20"/>
+        <v>600</v>
+      </c>
+      <c r="I47" s="4">
+        <f t="shared" si="20"/>
+        <v>750</v>
+      </c>
+      <c r="J47" s="4">
+        <f t="shared" si="20"/>
+        <v>937.5</v>
+      </c>
+      <c r="K47" s="4">
+        <f t="shared" si="20"/>
+        <v>1218.75</v>
+      </c>
+      <c r="L47" s="4">
+        <f t="shared" si="20"/>
+        <v>1443.75</v>
+      </c>
+      <c r="M47" s="4">
+        <f t="shared" si="20"/>
+        <v>1687.5</v>
+      </c>
+      <c r="N47" s="4">
+        <f t="shared" si="20"/>
+        <v>1837.5</v>
+      </c>
+      <c r="O47" s="4">
+        <f t="shared" si="20"/>
+        <v>2362.5</v>
+      </c>
+      <c r="P47" s="4">
+        <f t="shared" si="20"/>
+        <v>2681.25</v>
+      </c>
+      <c r="Q47" s="4">
+        <f t="shared" si="20"/>
+        <v>2850</v>
+      </c>
+      <c r="R47" s="4">
+        <f t="shared" si="20"/>
+        <v>3037.5</v>
+      </c>
+      <c r="S47" s="4">
+        <f t="shared" si="20"/>
+        <v>3543.75</v>
+      </c>
+      <c r="T47" s="4">
+        <f t="shared" si="20"/>
+        <v>3918.75</v>
+      </c>
+      <c r="U47" s="4">
+        <f t="shared" si="20"/>
+        <v>4312.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A48" s="8">
+        <f t="shared" si="19"/>
+        <v>30</v>
+      </c>
+      <c r="E48" s="4">
+        <f>$P$2*$A$48*((E20+1)*E5+(E27+1)*E6)</f>
+        <v>315</v>
+      </c>
+      <c r="F48" s="4">
+        <f t="shared" ref="F48:U48" si="21">$P$2*$A$48*((F20+1)*F5+(F27+1)*F6)</f>
+        <v>472.5</v>
+      </c>
+      <c r="G48" s="4">
+        <f t="shared" si="21"/>
+        <v>675</v>
+      </c>
+      <c r="H48" s="4">
+        <f t="shared" si="21"/>
+        <v>810</v>
+      </c>
+      <c r="I48" s="4">
+        <f t="shared" si="21"/>
+        <v>990</v>
+      </c>
+      <c r="J48" s="4">
+        <f t="shared" si="21"/>
+        <v>1215</v>
+      </c>
+      <c r="K48" s="4">
+        <f t="shared" si="21"/>
+        <v>1575</v>
+      </c>
+      <c r="L48" s="4">
+        <f t="shared" si="21"/>
+        <v>2002.5</v>
+      </c>
+      <c r="M48" s="4">
+        <f t="shared" si="21"/>
+        <v>2160</v>
+      </c>
+      <c r="N48" s="4">
+        <f t="shared" si="21"/>
+        <v>2340</v>
+      </c>
+      <c r="O48" s="4">
+        <f t="shared" si="21"/>
+        <v>2992.5</v>
+      </c>
+      <c r="P48" s="4">
+        <f t="shared" si="21"/>
+        <v>3217.5</v>
+      </c>
+      <c r="Q48" s="4">
+        <f t="shared" si="21"/>
+        <v>3600</v>
+      </c>
+      <c r="R48" s="4">
+        <f t="shared" si="21"/>
+        <v>3825</v>
+      </c>
+      <c r="S48" s="4">
+        <f t="shared" si="21"/>
+        <v>4455</v>
+      </c>
+      <c r="T48" s="4">
+        <f t="shared" si="21"/>
+        <v>5130</v>
+      </c>
+      <c r="U48" s="4">
+        <f t="shared" si="21"/>
+        <v>5625</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A49" s="8">
+        <f t="shared" si="19"/>
+        <v>35</v>
+      </c>
+      <c r="E49" s="4">
+        <f>$P$2*$A$49*((E21+1)*E5+(E28+1)*E6)</f>
+        <v>367.5</v>
+      </c>
+      <c r="F49" s="4">
+        <f t="shared" ref="F49:U49" si="22">$P$2*$A$49*((F21+1)*F5+(F28+1)*F6)</f>
         <v>630</v>
       </c>
-      <c r="I46" s="4">
-        <f>$P$2*$A$46*((I18+1)+(I25+1))</f>
-        <v>700</v>
-      </c>
-      <c r="J46" s="4">
-        <f>$P$2*$A$46*((J18+1)+(J25+1))</f>
-        <v>700</v>
-      </c>
-      <c r="K46" s="4">
-        <f>$P$2*$A$46*((K18+1)+(K25+1))</f>
-        <v>840</v>
-      </c>
-      <c r="L46" s="4">
-        <f>$P$2*$A$46*((L18+1)+(L25+1))</f>
-        <v>910</v>
-      </c>
-      <c r="M46" s="4">
-        <f>$P$2*$A$46*((M18+1)+(M25+1))</f>
-        <v>980</v>
-      </c>
-      <c r="N46" s="4">
-        <f>$P$2*$A$46*((N18+1)+(N25+1))</f>
-        <v>1050</v>
-      </c>
-      <c r="O46" s="4">
-        <f>$P$2*$A$46*((O18+1)+(O25+1))</f>
-        <v>1120</v>
-      </c>
-      <c r="P46" s="4">
-        <f>$P$2*$A$46*((P18+1)+(P25+1))</f>
-        <v>1190</v>
-      </c>
-      <c r="Q46" s="22">
-        <f>$P$2*$A$46*((Q18+1)+(Q25+1))</f>
+      <c r="G49" s="4">
+        <f t="shared" si="22"/>
+        <v>787.5</v>
+      </c>
+      <c r="H49" s="4">
+        <f t="shared" si="22"/>
+        <v>1023.75</v>
+      </c>
+      <c r="I49" s="4">
+        <f t="shared" si="22"/>
         <v>1260</v>
       </c>
-      <c r="R46" s="4">
-        <f>$P$2*$A$46*((R18+1)+(R25+1))</f>
-        <v>1330</v>
-      </c>
-      <c r="S46" s="4">
-        <f>$P$2*$A$46*((S18+1)+(S25+1))</f>
-        <v>1400</v>
-      </c>
-      <c r="T46" s="4">
-        <f>$P$2*$A$46*((T18+1)+(T25+1))</f>
-        <v>1470</v>
-      </c>
-      <c r="U46" s="4">
-        <f>$P$2*$A$46*((U18+1)+(U25+1))</f>
-        <v>1540</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="8">
-        <f t="shared" ref="A47:A49" si="15">A40</f>
-        <v>25</v>
-      </c>
-      <c r="E47" s="4">
-        <f>$P$2*$A$47*((E19+1)+(E26+1))</f>
-        <v>525</v>
-      </c>
-      <c r="F47" s="4">
-        <f>$P$2*$A$47*((F19+1)+(F26+1))</f>
-        <v>612.5</v>
-      </c>
-      <c r="G47" s="4">
-        <f>$P$2*$A$47*((G19+1)+(G26+1))</f>
-        <v>700</v>
-      </c>
-      <c r="H47" s="4">
-        <f>$P$2*$A$47*((H19+1)+(H26+1))</f>
-        <v>787.5</v>
-      </c>
-      <c r="I47" s="4">
-        <f>$P$2*$A$47*((I19+1)+(I26+1))</f>
-        <v>875</v>
-      </c>
-      <c r="J47" s="4">
-        <f>$P$2*$A$47*((J19+1)+(J26+1))</f>
-        <v>962.5</v>
-      </c>
-      <c r="K47" s="4">
-        <f>$P$2*$A$47*((K19+1)+(K26+1))</f>
-        <v>1137.5</v>
-      </c>
-      <c r="L47" s="4">
-        <f>$P$2*$A$47*((L19+1)+(L26+1))</f>
-        <v>1225</v>
-      </c>
-      <c r="M47" s="4">
-        <f>$P$2*$A$47*((M19+1)+(M26+1))</f>
-        <v>1312.5</v>
-      </c>
-      <c r="N47" s="4">
-        <f>$P$2*$A$47*((N19+1)+(N26+1))</f>
-        <v>1312.5</v>
-      </c>
-      <c r="O47" s="4">
-        <f>$P$2*$A$47*((O19+1)+(O26+1))</f>
-        <v>1575</v>
-      </c>
-      <c r="P47" s="4">
-        <f>$P$2*$A$47*((P19+1)+(P26+1))</f>
-        <v>1662.5</v>
-      </c>
-      <c r="Q47" s="22">
-        <f>$P$2*$A$47*((Q19+1)+(Q26+1))</f>
-        <v>1662.5</v>
-      </c>
-      <c r="R47" s="4">
-        <f>$P$2*$A$47*((R19+1)+(R26+1))</f>
-        <v>1662.5</v>
-      </c>
-      <c r="S47" s="4">
-        <f>$P$2*$A$47*((S19+1)+(S26+1))</f>
-        <v>1837.5</v>
-      </c>
-      <c r="T47" s="4">
-        <f>$P$2*$A$47*((T19+1)+(T26+1))</f>
-        <v>1925</v>
-      </c>
-      <c r="U47" s="4">
-        <f>$P$2*$A$47*((U19+1)+(U26+1))</f>
-        <v>2012.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="8">
-        <f t="shared" si="15"/>
-        <v>30</v>
-      </c>
-      <c r="E48" s="4">
-        <f>$P$2*$A$48*((E20+1)+(E27+1))</f>
-        <v>735</v>
-      </c>
-      <c r="F48" s="4">
-        <f>$P$2*$A$48*((F20+1)+(F27+1))</f>
-        <v>840</v>
-      </c>
-      <c r="G48" s="4">
-        <f>$P$2*$A$48*((G20+1)+(G27+1))</f>
-        <v>945</v>
-      </c>
-      <c r="H48" s="4">
-        <f>$P$2*$A$48*((H20+1)+(H27+1))</f>
-        <v>1050</v>
-      </c>
-      <c r="I48" s="4">
-        <f>$P$2*$A$48*((I20+1)+(I27+1))</f>
-        <v>1155</v>
-      </c>
-      <c r="J48" s="4">
-        <f>$P$2*$A$48*((J20+1)+(J27+1))</f>
-        <v>1260</v>
-      </c>
-      <c r="K48" s="4">
-        <f>$P$2*$A$48*((K20+1)+(K27+1))</f>
-        <v>1470</v>
-      </c>
-      <c r="L48" s="4">
-        <f>$P$2*$A$48*((L20+1)+(L27+1))</f>
-        <v>1680</v>
-      </c>
-      <c r="M48" s="4">
-        <f>$P$2*$A$48*((M20+1)+(M27+1))</f>
-        <v>1680</v>
-      </c>
-      <c r="N48" s="4">
-        <f>$P$2*$A$48*((N20+1)+(N27+1))</f>
-        <v>1680</v>
-      </c>
-      <c r="O48" s="4">
-        <f>$P$2*$A$48*((O20+1)+(O27+1))</f>
-        <v>1995</v>
-      </c>
-      <c r="P48" s="4">
-        <f>$P$2*$A$48*((P20+1)+(P27+1))</f>
-        <v>1995</v>
-      </c>
-      <c r="Q48" s="22">
-        <f>$P$2*$A$48*((Q20+1)+(Q27+1))</f>
-        <v>2100</v>
-      </c>
-      <c r="R48" s="4">
-        <f>$P$2*$A$48*((R20+1)+(R27+1))</f>
-        <v>2100</v>
-      </c>
-      <c r="S48" s="4">
-        <f>$P$2*$A$48*((S20+1)+(S27+1))</f>
+      <c r="J49" s="4">
+        <f t="shared" si="22"/>
+        <v>1548.75</v>
+      </c>
+      <c r="K49" s="4">
+        <f t="shared" si="22"/>
+        <v>1968.75</v>
+      </c>
+      <c r="L49" s="4">
+        <f t="shared" si="22"/>
         <v>2310</v>
       </c>
-      <c r="T48" s="4">
-        <f>$P$2*$A$48*((T20+1)+(T27+1))</f>
-        <v>2520</v>
-      </c>
-      <c r="U48" s="4">
-        <f>$P$2*$A$48*((U20+1)+(U27+1))</f>
-        <v>2625</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="8">
-        <f t="shared" si="15"/>
-        <v>35</v>
-      </c>
-      <c r="E49" s="4">
-        <f>$P$2*$A$49*((E21+1)+(E28+1))</f>
-        <v>857.5</v>
-      </c>
-      <c r="F49" s="4">
-        <f>$P$2*$A$49*((F21+1)+(F28+1))</f>
-        <v>1102.5</v>
-      </c>
-      <c r="G49" s="4">
-        <f>$P$2*$A$49*((G21+1)+(G28+1))</f>
-        <v>1102.5</v>
-      </c>
-      <c r="H49" s="4">
-        <f>$P$2*$A$49*((H21+1)+(H28+1))</f>
-        <v>1347.5</v>
-      </c>
-      <c r="I49" s="4">
-        <f>$P$2*$A$49*((I21+1)+(I28+1))</f>
-        <v>1470</v>
-      </c>
-      <c r="J49" s="4">
-        <f>$P$2*$A$49*((J21+1)+(J28+1))</f>
-        <v>1592.5</v>
-      </c>
-      <c r="K49" s="4">
-        <f>$P$2*$A$49*((K21+1)+(K28+1))</f>
-        <v>1837.5</v>
-      </c>
-      <c r="L49" s="4">
-        <f>$P$2*$A$49*((L21+1)+(L28+1))</f>
-        <v>1960</v>
-      </c>
       <c r="M49" s="4">
-        <f>$P$2*$A$49*((M21+1)+(M28+1))</f>
-        <v>2082.5</v>
+        <f t="shared" si="22"/>
+        <v>2677.5</v>
       </c>
       <c r="N49" s="4">
-        <f>$P$2*$A$49*((N21+1)+(N28+1))</f>
-        <v>2082.5</v>
+        <f t="shared" si="22"/>
+        <v>2913.75</v>
       </c>
       <c r="O49" s="4">
-        <f>$P$2*$A$49*((O21+1)+(O28+1))</f>
-        <v>2450</v>
+        <f t="shared" si="22"/>
+        <v>3675</v>
       </c>
       <c r="P49" s="4">
-        <f>$P$2*$A$49*((P21+1)+(P28+1))</f>
-        <v>2572.5</v>
-      </c>
-      <c r="Q49" s="22">
-        <f>$P$2*$A$49*((Q21+1)+(Q28+1))</f>
-        <v>2695</v>
+        <f t="shared" si="22"/>
+        <v>4147.5</v>
+      </c>
+      <c r="Q49" s="4">
+        <f t="shared" si="22"/>
+        <v>4620</v>
       </c>
       <c r="R49" s="4">
-        <f>$P$2*$A$49*((R21+1)+(R28+1))</f>
-        <v>2695</v>
+        <f t="shared" si="22"/>
+        <v>4908.75</v>
       </c>
       <c r="S49" s="4">
-        <f>$P$2*$A$49*((S21+1)+(S28+1))</f>
-        <v>2817.5</v>
+        <f t="shared" si="22"/>
+        <v>5433.75</v>
       </c>
       <c r="T49" s="4">
-        <f>$P$2*$A$49*((T21+1)+(T28+1))</f>
-        <v>3062.5</v>
+        <f t="shared" si="22"/>
+        <v>6247.5</v>
       </c>
       <c r="U49" s="4">
-        <f>$P$2*$A$49*((U21+1)+(U28+1))</f>
-        <v>3307.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="shared" si="22"/>
+        <v>7087.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" s="10">
         <f>A45</f>
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D52" s="15">
-        <f>D38*$L$2*A52</f>
-        <v>660</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+        <f>$A$53*D38*$L$2*$L$3/100</f>
+        <v>749.76</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <f>A46</f>
         <v>20</v>
@@ -4097,63 +4105,63 @@
         <v>499.84</v>
       </c>
       <c r="F53" s="15">
-        <f t="shared" ref="F53:U53" si="16">$A$53*F39*$L$2*$L$3/100</f>
+        <f t="shared" ref="F53:T53" si="23">$A$53*F39*$L$2*$L$3/100</f>
         <v>624.80000000000007</v>
       </c>
       <c r="G53" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>624.80000000000007</v>
       </c>
       <c r="H53" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>874.72</v>
       </c>
       <c r="I53" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>999.68</v>
       </c>
       <c r="J53" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>999.68</v>
       </c>
       <c r="K53" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>1249.6000000000001</v>
       </c>
       <c r="L53" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>1374.5600000000004</v>
       </c>
       <c r="M53" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>1499.52</v>
       </c>
       <c r="N53" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>1624.48</v>
       </c>
       <c r="O53" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>1749.44</v>
       </c>
       <c r="P53" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>1874.4</v>
       </c>
-      <c r="Q53" s="23">
-        <f t="shared" si="16"/>
+      <c r="Q53" s="22">
+        <f t="shared" si="23"/>
         <v>1999.36</v>
       </c>
       <c r="R53" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>2124.3200000000002</v>
       </c>
       <c r="S53" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>2249.2800000000002</v>
       </c>
       <c r="T53" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>2374.2400000000002</v>
       </c>
       <c r="U53" s="15">
@@ -4161,9 +4169,9 @@
         <v>2499.2000000000003</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" s="8">
-        <f t="shared" ref="A54:A56" si="17">A47</f>
+        <f t="shared" ref="A54:A56" si="24">A47</f>
         <v>25</v>
       </c>
       <c r="D54" s="15"/>
@@ -4172,73 +4180,73 @@
         <v>624.80000000000007</v>
       </c>
       <c r="F54" s="15">
-        <f t="shared" ref="F54:U54" si="18">$A$54*F40*$L$2*$L$3/100</f>
+        <f t="shared" ref="F54:U54" si="25">$A$54*F40*$L$2*$L$3/100</f>
         <v>781</v>
       </c>
       <c r="G54" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>937.2</v>
       </c>
       <c r="H54" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>1093.4000000000001</v>
       </c>
       <c r="I54" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>1249.6000000000001</v>
       </c>
       <c r="J54" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>1405.8000000000002</v>
       </c>
       <c r="K54" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>1718.2</v>
       </c>
       <c r="L54" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>1874.4</v>
       </c>
       <c r="M54" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>2030.6000000000004</v>
       </c>
       <c r="N54" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>2030.6000000000004</v>
       </c>
       <c r="O54" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>2499.2000000000003</v>
       </c>
       <c r="P54" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>2655.4000000000005</v>
       </c>
-      <c r="Q54" s="23">
-        <f t="shared" si="18"/>
+      <c r="Q54" s="22">
+        <f t="shared" si="25"/>
         <v>2655.4000000000005</v>
       </c>
       <c r="R54" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>2655.4000000000005</v>
       </c>
       <c r="S54" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>2967.8</v>
       </c>
       <c r="T54" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>3124</v>
       </c>
       <c r="U54" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>3280.2</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>30</v>
       </c>
       <c r="D55" s="15"/>
@@ -4247,73 +4255,73 @@
         <v>937.2</v>
       </c>
       <c r="F55" s="15">
-        <f t="shared" ref="F55:U55" si="19">$A$55*F41*$L$2*$L$3/100</f>
+        <f t="shared" ref="F55:U55" si="26">$A$55*F41*$L$2*$L$3/100</f>
         <v>1124.6400000000001</v>
       </c>
       <c r="G55" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>1312.0800000000004</v>
       </c>
       <c r="H55" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>1499.52</v>
       </c>
       <c r="I55" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>1686.96</v>
       </c>
       <c r="J55" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>1874.4</v>
       </c>
       <c r="K55" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>2249.2800000000002</v>
       </c>
       <c r="L55" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>2624.1600000000008</v>
       </c>
       <c r="M55" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>2624.1600000000008</v>
       </c>
       <c r="N55" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>2624.1600000000008</v>
       </c>
       <c r="O55" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>3186.48</v>
       </c>
       <c r="P55" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>3186.48</v>
       </c>
-      <c r="Q55" s="23">
-        <f t="shared" si="19"/>
+      <c r="Q55" s="22">
+        <f t="shared" si="26"/>
         <v>3373.92</v>
       </c>
       <c r="R55" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>3373.92</v>
       </c>
       <c r="S55" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>3748.8</v>
       </c>
       <c r="T55" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>4123.68</v>
       </c>
       <c r="U55" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>4311.1200000000008</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>35</v>
       </c>
       <c r="D56" s="15"/>
@@ -4322,71 +4330,71 @@
         <v>1093.4000000000001</v>
       </c>
       <c r="F56" s="15">
-        <f t="shared" ref="F56:U56" si="20">$A$56*F42*$L$2*$L$3/100</f>
+        <f t="shared" ref="F56:U56" si="27">$A$56*F42*$L$2*$L$3/100</f>
         <v>1530.76</v>
       </c>
       <c r="G56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>1530.76</v>
       </c>
       <c r="H56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>1968.12</v>
       </c>
       <c r="I56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>2186.8000000000002</v>
       </c>
       <c r="J56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>2405.4800000000005</v>
       </c>
       <c r="K56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>2842.8400000000006</v>
       </c>
       <c r="L56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>3061.52</v>
       </c>
       <c r="M56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>3280.2</v>
       </c>
       <c r="N56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>3280.2</v>
       </c>
       <c r="O56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>3936.24</v>
       </c>
       <c r="P56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>4154.920000000001</v>
       </c>
-      <c r="Q56" s="23">
-        <f t="shared" si="20"/>
+      <c r="Q56" s="22">
+        <f t="shared" si="27"/>
         <v>4373.6000000000004</v>
       </c>
       <c r="R56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>4373.6000000000004</v>
       </c>
       <c r="S56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>4592.2800000000007</v>
       </c>
       <c r="T56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>5029.6400000000003</v>
       </c>
       <c r="U56" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>5467.0000000000009</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
       <c r="D61" t="s">
         <v>48</v>
       </c>
@@ -4395,7 +4403,7 @@
         <v>135.42486889354092</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
       <c r="D62" t="s">
         <v>45</v>
       </c>
@@ -4403,7 +4411,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="D63" t="s">
         <v>46</v>
       </c>
@@ -4411,7 +4419,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.35">
       <c r="F67" s="8" t="s">
         <v>35</v>
       </c>
@@ -4422,23 +4430,23 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.35">
       <c r="E68" t="s">
         <v>52</v>
       </c>
-      <c r="F68" s="25">
+      <c r="F68" s="24">
         <v>4</v>
       </c>
-      <c r="G68" s="25">
+      <c r="G68" s="24">
         <f>2.25*2.25</f>
         <v>5.0625</v>
       </c>
-      <c r="H68" s="25">
+      <c r="H68" s="24">
         <f>2.5*2.5</f>
         <v>6.25</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
         <v>54</v>
       </c>
@@ -4447,21 +4455,21 @@
       </c>
       <c r="F69" s="4">
         <f>Q46+$H$2</f>
-        <v>1760</v>
+        <v>2660</v>
       </c>
       <c r="G69" s="15">
         <f>S46+$H$2</f>
-        <v>1900</v>
+        <v>3200</v>
       </c>
       <c r="H69" s="4">
         <f>U46+$H$2</f>
-        <v>2040</v>
+        <v>3800</v>
       </c>
       <c r="J69" s="4"/>
       <c r="K69" s="15"/>
       <c r="L69" s="4"/>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>56</v>
       </c>
@@ -4469,47 +4477,47 @@
         <v>50</v>
       </c>
       <c r="F70" s="4">
-        <f t="shared" ref="F70:F71" si="21">Q47+$H$2</f>
-        <v>2162.5</v>
+        <f t="shared" ref="F70:F71" si="28">Q47+$H$2</f>
+        <v>3350</v>
       </c>
       <c r="G70" s="15">
         <f>S47+$H$2</f>
-        <v>2337.5</v>
+        <v>4043.75</v>
       </c>
       <c r="H70" s="4">
-        <f t="shared" ref="H70:H71" si="22">U47+$H$2</f>
-        <v>2512.5</v>
+        <f t="shared" ref="H70:H71" si="29">U47+$H$2</f>
+        <v>4812.5</v>
       </c>
       <c r="J70" s="4"/>
       <c r="K70" s="15"/>
       <c r="L70" s="4"/>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.35">
       <c r="E71" t="s">
         <v>51</v>
       </c>
       <c r="F71" s="4">
-        <f t="shared" si="21"/>
-        <v>2600</v>
+        <f t="shared" si="28"/>
+        <v>4100</v>
       </c>
       <c r="G71" s="15">
         <f>S48+$H$2</f>
-        <v>2810</v>
+        <v>4955</v>
       </c>
       <c r="H71" s="4">
-        <f t="shared" si="22"/>
-        <v>3125</v>
+        <f t="shared" si="29"/>
+        <v>6125</v>
       </c>
       <c r="J71" s="4"/>
       <c r="K71" s="15"/>
       <c r="L71" s="4"/>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.35">
       <c r="E73" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.35">
       <c r="E74" t="s">
         <v>49</v>
       </c>
@@ -4517,55 +4525,55 @@
         <f>Q10</f>
         <v>2080</v>
       </c>
-      <c r="G74" s="24">
+      <c r="G74" s="23">
         <f>S10</f>
         <v>2632.5</v>
       </c>
-      <c r="H74" s="24">
+      <c r="H74" s="23">
         <f>U10</f>
         <v>3250</v>
       </c>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:12" x14ac:dyDescent="0.35">
       <c r="E75" t="s">
         <v>50</v>
       </c>
       <c r="F75" s="8">
-        <f t="shared" ref="F75:F76" si="23">Q11</f>
+        <f t="shared" ref="F75:F76" si="30">Q11</f>
         <v>2600</v>
       </c>
-      <c r="G75" s="24">
-        <f t="shared" ref="G75:G76" si="24">S11</f>
+      <c r="G75" s="23">
+        <f t="shared" ref="G75:G76" si="31">S11</f>
         <v>3290.625</v>
       </c>
-      <c r="H75" s="24">
-        <f t="shared" ref="H75:H76" si="25">U11</f>
+      <c r="H75" s="23">
+        <f t="shared" ref="H75:H76" si="32">U11</f>
         <v>4062.5</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.35">
       <c r="E76" t="s">
         <v>51</v>
       </c>
       <c r="F76" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>3120</v>
       </c>
-      <c r="G76" s="24">
-        <f t="shared" si="24"/>
+      <c r="G76" s="23">
+        <f t="shared" si="31"/>
         <v>3948.75</v>
       </c>
-      <c r="H76" s="24">
-        <f t="shared" si="25"/>
+      <c r="H76" s="23">
+        <f t="shared" si="32"/>
         <v>4875</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.35">
       <c r="D78" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>59</v>
       </c>
@@ -4573,22 +4581,23 @@
         <v>250</v>
       </c>
     </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>58</v>
       </c>
       <c r="G81" s="17">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+        <f>8*35*P2</f>
+        <v>840</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>57</v>
       </c>
       <c r="E82" s="4"/>
       <c r="G82" s="4">
-        <f>(120*5+260*3)*0.2*P2</f>
-        <v>966</v>
+        <f>(120*4+260*5)*0.2*P2</f>
+        <v>1068</v>
       </c>
     </row>
   </sheetData>

--- a/Ostalo/kalkulacije.xlsx
+++ b/Ostalo/kalkulacije.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HT-ICT\Documents\GitHub\KalkulacijeGradjevina\Ostalo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\KalkulacijeGradjevina\Ostalo\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E2A3CC-05F4-4804-B74F-D2DF317274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bušenje" sheetId="1" r:id="rId1"/>
     <sheet name="Rezanje stropa" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
   <si>
     <t>dolazak</t>
   </si>
@@ -123,9 +124,6 @@
     <t>1m2</t>
   </si>
   <si>
-    <t>cijena reza</t>
-  </si>
-  <si>
     <t>komadi 40-60kg</t>
   </si>
   <si>
@@ -141,39 +139,6 @@
     <t>otvor dimenzije u metrima</t>
   </si>
   <si>
-    <t>cijena dana</t>
-  </si>
-  <si>
-    <t>cijena rupe</t>
-  </si>
-  <si>
-    <t>cijena rupa</t>
-  </si>
-  <si>
-    <t>cijena rezanja</t>
-  </si>
-  <si>
-    <t>promjer rupe</t>
-  </si>
-  <si>
-    <t>broj redova bloka</t>
-  </si>
-  <si>
-    <t>broj koluma bloka</t>
-  </si>
-  <si>
-    <t>veličina rezne ploče u mm</t>
-  </si>
-  <si>
-    <t>debljina zida u mm</t>
-  </si>
-  <si>
-    <t>težina bloka u kg</t>
-  </si>
-  <si>
-    <t>formula za over cut u mm</t>
-  </si>
-  <si>
     <t>20cm</t>
   </si>
   <si>
@@ -205,12 +170,60 @@
   </si>
   <si>
     <t>rezanje zida (prozor) opeka otvoru 1,0*1,0*35</t>
+  </si>
+  <si>
+    <t>m2=</t>
+  </si>
+  <si>
+    <t>Jediniučna cijena rezanja:</t>
+  </si>
+  <si>
+    <t>Jedinična cijena bušenja</t>
+  </si>
+  <si>
+    <t>Broj redova bloka:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broj koluma blok: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cijena rezanja: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cijena rupa: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Težina bloka u kg: </t>
+  </si>
+  <si>
+    <t>Broj rupa kod rastera :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Težina ukupna u kg: </t>
+  </si>
+  <si>
+    <t>Cijena dana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula za over cut u mm: </t>
+  </si>
+  <si>
+    <t>Veličina rezne ploče u mm:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debljina zida u mm: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dodatni poslovi: </t>
+  </si>
+  <si>
+    <t>Ukupan iznos:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;kn&quot;_-;\-* #,##0.00\ &quot;kn&quot;_-;_-* &quot;-&quot;??\ &quot;kn&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -298,7 +311,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -325,7 +338,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -351,12 +363,26 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Normalno" xfId="0" builtinId="0"/>
+    <cellStyle name="Postotak" xfId="1" builtinId="5"/>
+    <cellStyle name="Valuta" xfId="3" builtinId="4"/>
+    <cellStyle name="Zarez" xfId="2" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -667,24 +693,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S48"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.26953125" customWidth="1"/>
-    <col min="2" max="2" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.453125" customWidth="1"/>
-    <col min="12" max="12" width="22.81640625" customWidth="1"/>
-    <col min="17" max="17" width="22.26953125" customWidth="1"/>
+    <col min="7" max="7" width="22.42578125" customWidth="1"/>
+    <col min="12" max="12" width="22.85546875" customWidth="1"/>
+    <col min="17" max="17" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -726,7 +752,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
@@ -771,7 +797,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
@@ -816,7 +842,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
@@ -861,7 +887,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>21</v>
       </c>
@@ -906,7 +932,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>25</v>
       </c>
@@ -951,7 +977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>1</v>
       </c>
@@ -996,7 +1022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C12" s="6" t="s">
         <v>26</v>
       </c>
@@ -1029,7 +1055,7 @@
         <v>102.12</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B15" t="str">
         <f t="shared" ref="B15:B20" si="3">B6</f>
         <v>promjer rupe mm</v>
@@ -1075,7 +1101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B16" t="str">
         <f t="shared" si="3"/>
         <v>vrsta bušenja</v>
@@ -1121,7 +1147,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B17" t="str">
         <f t="shared" si="3"/>
         <v>dubina ukupna cm</v>
@@ -1167,7 +1193,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
         <f t="shared" si="3"/>
         <v>zaštita (0-NE; 1-DA)</v>
@@ -1213,7 +1239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">ankerisanje </v>
@@ -1259,7 +1285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B20" t="str">
         <f t="shared" si="3"/>
         <v>broj rupa</v>
@@ -1305,7 +1331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C21" t="str">
         <f>C12</f>
         <v>Ukupno:</v>
@@ -1339,7 +1365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B24" t="str">
         <f>B15</f>
         <v>promjer rupe mm</v>
@@ -1385,7 +1411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B25" t="str">
         <f>B16</f>
         <v>vrsta bušenja</v>
@@ -1431,7 +1457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B26" t="str">
         <f>B17</f>
         <v>dubina ukupna cm</v>
@@ -1477,7 +1503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B27" t="str">
         <f>B9</f>
         <v>zaštita (0-NE; 1-DA)</v>
@@ -1523,7 +1549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B28" t="str">
         <f t="shared" ref="B28:B29" si="10">B19</f>
         <v xml:space="preserve">ankerisanje </v>
@@ -1569,7 +1595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B29" t="str">
         <f t="shared" si="10"/>
         <v>broj rupa</v>
@@ -1615,7 +1641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C30" t="str">
         <f>C21</f>
         <v>Ukupno:</v>
@@ -1653,7 +1679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>15</v>
       </c>
@@ -1686,7 +1712,7 @@
         <v>122.12</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>18</v>
       </c>
@@ -1725,7 +1751,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C34" s="3" t="s">
         <v>17</v>
       </c>
@@ -1756,7 +1782,7 @@
         <v>116.01400000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>2</v>
       </c>
@@ -1777,7 +1803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>20</v>
       </c>
@@ -1803,7 +1829,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="F40">
         <v>2</v>
       </c>
@@ -1823,7 +1849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>0</v>
       </c>
@@ -1843,7 +1869,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1</v>
       </c>
@@ -1866,7 +1892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2</v>
       </c>
@@ -1895,7 +1921,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>3</v>
       </c>
@@ -1924,7 +1950,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>4</v>
       </c>
@@ -1953,10 +1979,10 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C48" s="1"/>
     </row>
   </sheetData>
@@ -1965,2639 +1991,2694 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U82"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:U91"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" customWidth="1"/>
-    <col min="3" max="3" width="6.453125" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="11.1796875" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="16" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.1796875" style="18" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.7265625" customWidth="1"/>
+    <col min="10" max="16" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="P1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="9">
         <v>2600</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="14">
-        <v>500</v>
+        <v>58</v>
+      </c>
+      <c r="H2" s="27">
+        <v>0</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" s="15">
+        <v>50</v>
+      </c>
+      <c r="L2" s="28">
         <v>2.2000000000000002</v>
       </c>
       <c r="O2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="P2" s="27">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="K3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="9">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="M4" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="K3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="M4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="9">
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="12">
+        <f>D12/(D10*D11)</f>
+        <v>58.5</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P6" s="11">
+        <f>P7/2-SQRT((P7/2)*(P7/2)-((D9*10)*(D9*10)))</f>
+        <v>87.750100080080074</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D7" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="22">
+        <f>(D10+1)*2+(D11-1)*2</f>
+        <v>8</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P7" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="8">
+        <f>D6*D7</f>
+        <v>0.36</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="O8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P8" s="9">
+        <f>D9*10</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C9" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="10">
+        <v>25</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="29">
+        <f>$P$2*D9*((D10+1)*D6+(D11+1)*D7)</f>
+        <v>198</v>
+      </c>
+      <c r="N9" s="15"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C10" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="10">
+        <v>2</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="29">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C11" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="10">
+        <v>2</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="30">
+        <f>$D$9*H7*$L$2*$L$3/100</f>
+        <v>448.80000000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C12" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="22">
+        <f>D8*D9/100*C2</f>
+        <v>234</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" s="4">
+        <f>H9+H10+H11</f>
+        <v>846.80000000000007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C14" s="3" t="str">
+        <f>C6</f>
+        <v>otvor dimenzije u metrima</v>
+      </c>
+      <c r="E14">
+        <v>0.5</v>
+      </c>
+      <c r="F14">
+        <v>0.5</v>
+      </c>
+      <c r="G14">
+        <v>0.5</v>
+      </c>
+      <c r="H14">
+        <v>0.75</v>
+      </c>
+      <c r="I14">
         <v>1</v>
       </c>
-      <c r="E5">
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1.25</v>
+      </c>
+      <c r="L14">
+        <v>1.25</v>
+      </c>
+      <c r="M14">
+        <v>1.5</v>
+      </c>
+      <c r="N14">
+        <v>1.5</v>
+      </c>
+      <c r="O14">
+        <v>1.75</v>
+      </c>
+      <c r="P14">
+        <v>1.75</v>
+      </c>
+      <c r="Q14" s="17">
+        <v>2</v>
+      </c>
+      <c r="R14">
+        <v>2</v>
+      </c>
+      <c r="S14">
+        <v>2.25</v>
+      </c>
+      <c r="T14">
+        <v>2.25</v>
+      </c>
+      <c r="U14">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="E15">
         <v>0.5</v>
       </c>
-      <c r="F5">
-        <v>0.5</v>
-      </c>
-      <c r="G5">
-        <v>0.5</v>
-      </c>
-      <c r="H5">
+      <c r="F15">
         <v>0.75</v>
       </c>
-      <c r="I5">
+      <c r="G15">
         <v>1</v>
       </c>
-      <c r="J5">
+      <c r="H15">
         <v>1</v>
       </c>
-      <c r="K5">
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
         <v>1.25</v>
       </c>
-      <c r="L5">
+      <c r="K15">
         <v>1.25</v>
       </c>
-      <c r="M5">
+      <c r="L15">
         <v>1.5</v>
       </c>
-      <c r="N5">
+      <c r="M15">
         <v>1.5</v>
       </c>
-      <c r="O5">
+      <c r="N15">
         <v>1.75</v>
       </c>
-      <c r="P5">
+      <c r="O15">
         <v>1.75</v>
       </c>
-      <c r="Q5" s="18">
+      <c r="P15">
         <v>2</v>
       </c>
-      <c r="R5">
+      <c r="Q15" s="17">
         <v>2</v>
       </c>
-      <c r="S5">
+      <c r="R15">
         <v>2.25</v>
       </c>
-      <c r="T5">
+      <c r="S15">
         <v>2.25</v>
       </c>
-      <c r="U5">
+      <c r="T15">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="D6" s="9">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>0.5</v>
-      </c>
-      <c r="F6">
-        <v>0.75</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1.25</v>
-      </c>
-      <c r="K6">
-        <v>1.25</v>
-      </c>
-      <c r="L6">
-        <v>1.5</v>
-      </c>
-      <c r="M6">
-        <v>1.5</v>
-      </c>
-      <c r="N6">
-        <v>1.75</v>
-      </c>
-      <c r="O6">
-        <v>1.75</v>
-      </c>
-      <c r="P6">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="18">
-        <v>2</v>
-      </c>
-      <c r="R6">
-        <v>2.25</v>
-      </c>
-      <c r="S6">
-        <v>2.25</v>
-      </c>
-      <c r="T6">
+      <c r="U15">
         <v>2.5</v>
       </c>
-      <c r="U6">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="D7">
-        <f>D5*D6</f>
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <f>E6*E5</f>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="E16">
+        <f>E15*E14</f>
         <v>0.25</v>
       </c>
-      <c r="F7">
-        <f t="shared" ref="F7:U7" si="0">F6*F5</f>
+      <c r="F16">
+        <f t="shared" ref="F16:U16" si="0">F15*F14</f>
         <v>0.375</v>
       </c>
-      <c r="G7">
+      <c r="G16">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="H7">
+      <c r="H16">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
-      <c r="I7">
+      <c r="I16">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J7">
+      <c r="J16">
         <f t="shared" si="0"/>
         <v>1.25</v>
       </c>
-      <c r="K7">
+      <c r="K16">
         <f t="shared" si="0"/>
         <v>1.5625</v>
       </c>
-      <c r="L7">
+      <c r="L16">
         <f t="shared" si="0"/>
         <v>1.875</v>
       </c>
-      <c r="M7">
+      <c r="M16">
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
-      <c r="N7">
+      <c r="N16">
         <f t="shared" si="0"/>
         <v>2.625</v>
       </c>
-      <c r="O7">
+      <c r="O16">
         <f t="shared" si="0"/>
         <v>3.0625</v>
       </c>
-      <c r="P7">
+      <c r="P16">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="Q7" s="18">
+      <c r="Q16" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="R7">
+      <c r="R16">
         <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
-      <c r="S7">
+      <c r="S16">
         <f t="shared" si="0"/>
         <v>5.0625</v>
       </c>
-      <c r="T7">
+      <c r="T16">
         <f t="shared" si="0"/>
         <v>5.625</v>
       </c>
-      <c r="U7">
+      <c r="U16">
         <f t="shared" si="0"/>
         <v>6.25</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="8" t="s">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" t="str">
+        <f>C9</f>
+        <v xml:space="preserve">Debljina u cm: </v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A9" s="10">
-        <v>35</v>
-      </c>
-      <c r="B9">
-        <f>A9*$C$2/100</f>
-        <v>910</v>
-      </c>
-      <c r="D9">
-        <f>D7*A9/100*C2</f>
-        <v>909.99999999999989</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A10" s="8">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
+        <f>D9</f>
+        <v>25</v>
+      </c>
+      <c r="B18">
+        <f>D9*$C$2/100</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
         <v>20</v>
       </c>
-      <c r="B10">
-        <f>A10*$C$2/100</f>
+      <c r="B19">
+        <f>A19*$C$2/100</f>
         <v>520</v>
       </c>
-      <c r="E10">
-        <f>E$7*$A$10/100*$C$2</f>
+      <c r="E19">
+        <f>E$16*$A$19/100*$C$2</f>
         <v>130</v>
       </c>
-      <c r="F10">
-        <f t="shared" ref="F10:U10" si="1">F$7*$A$10/100*$C$2</f>
+      <c r="F19">
+        <f t="shared" ref="F19:U19" si="1">F$16*$A$19/100*$C$2</f>
         <v>195</v>
       </c>
-      <c r="G10">
+      <c r="G19">
         <f t="shared" si="1"/>
         <v>260</v>
       </c>
-      <c r="H10">
+      <c r="H19">
         <f t="shared" si="1"/>
         <v>390</v>
       </c>
-      <c r="I10">
+      <c r="I19">
         <f t="shared" si="1"/>
         <v>520</v>
       </c>
-      <c r="J10">
+      <c r="J19">
         <f t="shared" si="1"/>
         <v>650</v>
       </c>
-      <c r="K10">
+      <c r="K19">
         <f t="shared" si="1"/>
         <v>812.5</v>
       </c>
-      <c r="L10">
+      <c r="L19">
         <f t="shared" si="1"/>
         <v>975</v>
       </c>
-      <c r="M10">
+      <c r="M19">
         <f t="shared" si="1"/>
         <v>1170</v>
       </c>
-      <c r="N10">
+      <c r="N19">
         <f t="shared" si="1"/>
         <v>1365</v>
       </c>
-      <c r="O10">
+      <c r="O19">
         <f t="shared" si="1"/>
         <v>1592.5000000000002</v>
       </c>
-      <c r="P10">
+      <c r="P19">
         <f t="shared" si="1"/>
         <v>1819.9999999999998</v>
       </c>
-      <c r="Q10" s="18">
+      <c r="Q19" s="17">
         <f t="shared" si="1"/>
         <v>2080</v>
       </c>
-      <c r="R10">
+      <c r="R19">
         <f t="shared" si="1"/>
         <v>2340</v>
       </c>
-      <c r="S10">
+      <c r="S19">
         <f t="shared" si="1"/>
         <v>2632.5</v>
       </c>
-      <c r="T10">
+      <c r="T19">
         <f t="shared" si="1"/>
         <v>2925</v>
       </c>
-      <c r="U10">
+      <c r="U19">
         <f t="shared" si="1"/>
         <v>3250</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A11" s="8">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
         <v>25</v>
       </c>
-      <c r="B11">
-        <f>A11*$C$2/100</f>
+      <c r="B20">
+        <f>A20*$C$2/100</f>
         <v>650</v>
       </c>
-      <c r="E11">
-        <f>E$7*$A$11/100*$C$2</f>
+      <c r="E20">
+        <f>E$16*$A$20/100*$C$2</f>
         <v>162.5</v>
       </c>
-      <c r="F11">
-        <f t="shared" ref="F11:U11" si="2">F$7*$A$11/100*$C$2</f>
+      <c r="F20">
+        <f t="shared" ref="F20:U20" si="2">F$16*$A$20/100*$C$2</f>
         <v>243.75</v>
       </c>
-      <c r="G11">
+      <c r="G20">
         <f t="shared" si="2"/>
         <v>325</v>
       </c>
-      <c r="H11">
+      <c r="H20">
         <f t="shared" si="2"/>
         <v>487.5</v>
       </c>
-      <c r="I11">
+      <c r="I20">
         <f t="shared" si="2"/>
         <v>650</v>
       </c>
-      <c r="J11">
+      <c r="J20">
         <f t="shared" si="2"/>
         <v>812.5</v>
       </c>
-      <c r="K11">
+      <c r="K20">
         <f t="shared" si="2"/>
         <v>1015.625</v>
       </c>
-      <c r="L11">
+      <c r="L20">
         <f t="shared" si="2"/>
         <v>1218.75</v>
       </c>
-      <c r="M11">
+      <c r="M20">
         <f t="shared" si="2"/>
         <v>1462.5</v>
       </c>
-      <c r="N11">
+      <c r="N20">
         <f t="shared" si="2"/>
         <v>1706.25</v>
       </c>
-      <c r="O11">
+      <c r="O20">
         <f t="shared" si="2"/>
         <v>1990.625</v>
       </c>
-      <c r="P11">
+      <c r="P20">
         <f t="shared" si="2"/>
         <v>2275</v>
       </c>
-      <c r="Q11" s="18">
+      <c r="Q20" s="17">
         <f t="shared" si="2"/>
         <v>2600</v>
       </c>
-      <c r="R11">
+      <c r="R20">
         <f t="shared" si="2"/>
         <v>2925</v>
       </c>
-      <c r="S11">
+      <c r="S20">
         <f t="shared" si="2"/>
         <v>3290.625</v>
       </c>
-      <c r="T11">
+      <c r="T20">
         <f t="shared" si="2"/>
         <v>3656.25</v>
       </c>
-      <c r="U11">
+      <c r="U20">
         <f t="shared" si="2"/>
         <v>4062.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A12" s="8">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
         <v>30</v>
       </c>
-      <c r="B12">
-        <f>A12*$C$2/100</f>
+      <c r="B21">
+        <f>A21*$C$2/100</f>
         <v>780</v>
       </c>
-      <c r="E12">
-        <f>E$7*$A$12/100*$C$2</f>
+      <c r="E21">
+        <f>E$16*$A$21/100*$C$2</f>
         <v>195</v>
       </c>
-      <c r="F12">
-        <f t="shared" ref="F12:U12" si="3">F$7*$A$12/100*$C$2</f>
+      <c r="F21">
+        <f t="shared" ref="F21:U21" si="3">F$16*$A$21/100*$C$2</f>
         <v>292.5</v>
       </c>
-      <c r="G12">
-        <f>G$7*$A$12/100*$C$2</f>
+      <c r="G21">
+        <f>G$16*$A$21/100*$C$2</f>
         <v>390</v>
       </c>
-      <c r="H12">
+      <c r="H21">
         <f t="shared" si="3"/>
         <v>585</v>
       </c>
-      <c r="I12">
+      <c r="I21">
         <f t="shared" si="3"/>
         <v>780</v>
       </c>
-      <c r="J12">
+      <c r="J21">
         <f t="shared" si="3"/>
         <v>975</v>
       </c>
-      <c r="K12">
+      <c r="K21">
         <f t="shared" si="3"/>
         <v>1218.75</v>
       </c>
-      <c r="L12">
+      <c r="L21">
         <f t="shared" si="3"/>
         <v>1462.5</v>
       </c>
-      <c r="M12">
+      <c r="M21">
         <f t="shared" si="3"/>
         <v>1755.0000000000002</v>
       </c>
-      <c r="N12">
+      <c r="N21">
         <f t="shared" si="3"/>
         <v>2047.5</v>
       </c>
-      <c r="O12">
+      <c r="O21">
         <f t="shared" si="3"/>
         <v>2388.75</v>
       </c>
-      <c r="P12">
+      <c r="P21">
         <f t="shared" si="3"/>
         <v>2730</v>
       </c>
-      <c r="Q12" s="18">
+      <c r="Q21" s="17">
         <f t="shared" si="3"/>
         <v>3120</v>
       </c>
-      <c r="R12">
+      <c r="R21">
         <f t="shared" si="3"/>
         <v>3510.0000000000005</v>
       </c>
-      <c r="S12">
+      <c r="S21">
         <f t="shared" si="3"/>
         <v>3948.75</v>
       </c>
-      <c r="T12">
+      <c r="T21">
         <f t="shared" si="3"/>
         <v>4387.5</v>
       </c>
-      <c r="U12">
+      <c r="U21">
         <f t="shared" si="3"/>
         <v>4875</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A13" s="8">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
         <v>35</v>
       </c>
-      <c r="B13">
-        <f>A13*$C$2/100</f>
+      <c r="B22">
+        <f>A22*$C$2/100</f>
         <v>910</v>
       </c>
-      <c r="E13">
-        <f>E$7*$A$13/100*$C$2</f>
+      <c r="E22">
+        <f>E$16*$A$22/100*$C$2</f>
         <v>227.49999999999997</v>
       </c>
-      <c r="F13">
-        <f t="shared" ref="F13:U13" si="4">F$7*$A$13/100*$C$2</f>
+      <c r="F22">
+        <f t="shared" ref="F22:U22" si="4">F$16*$A$22/100*$C$2</f>
         <v>341.25</v>
       </c>
-      <c r="G13">
+      <c r="G22">
         <f t="shared" si="4"/>
         <v>454.99999999999994</v>
       </c>
-      <c r="H13">
+      <c r="H22">
         <f t="shared" si="4"/>
         <v>682.5</v>
       </c>
-      <c r="I13">
+      <c r="I22">
         <f t="shared" si="4"/>
         <v>909.99999999999989</v>
       </c>
-      <c r="J13">
+      <c r="J22">
         <f t="shared" si="4"/>
         <v>1137.5</v>
       </c>
-      <c r="K13">
+      <c r="K22">
         <f t="shared" si="4"/>
         <v>1421.875</v>
       </c>
-      <c r="L13">
+      <c r="L22">
         <f t="shared" si="4"/>
         <v>1706.25</v>
       </c>
-      <c r="M13">
+      <c r="M22">
         <f t="shared" si="4"/>
         <v>2047.5</v>
       </c>
-      <c r="N13">
+      <c r="N22">
         <f t="shared" si="4"/>
         <v>2388.75</v>
       </c>
-      <c r="O13">
+      <c r="O22">
         <f t="shared" si="4"/>
         <v>2786.8749999999995</v>
       </c>
-      <c r="P13">
+      <c r="P22">
         <f t="shared" si="4"/>
         <v>3185.0000000000005</v>
       </c>
-      <c r="Q13" s="18">
+      <c r="Q22" s="17">
         <f t="shared" si="4"/>
         <v>3639.9999999999995</v>
       </c>
-      <c r="R13">
+      <c r="R22">
         <f t="shared" si="4"/>
         <v>4095</v>
       </c>
-      <c r="S13">
+      <c r="S22">
         <f t="shared" si="4"/>
         <v>4606.875</v>
       </c>
-      <c r="T13">
+      <c r="T22">
         <f t="shared" si="4"/>
         <v>5118.75</v>
       </c>
-      <c r="U13">
+      <c r="U22">
         <f t="shared" si="4"/>
         <v>5687.5</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="D16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A17" s="25">
-        <f>A9</f>
-        <v>35</v>
-      </c>
-      <c r="D17" s="9">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D25" t="str">
+        <f>C10</f>
+        <v>Broj redova bloka:</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" s="24"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <f>A19</f>
+        <v>20</v>
+      </c>
+      <c r="E27" s="13">
+        <v>2</v>
+      </c>
+      <c r="F27" s="13">
+        <v>2</v>
+      </c>
+      <c r="G27" s="13">
+        <v>2</v>
+      </c>
+      <c r="H27" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A18" s="8">
-        <f>A10</f>
-        <v>20</v>
-      </c>
-      <c r="E18" s="13">
+      <c r="I27" s="13">
+        <v>4</v>
+      </c>
+      <c r="J27" s="13">
+        <v>4</v>
+      </c>
+      <c r="K27" s="13">
+        <v>5</v>
+      </c>
+      <c r="L27" s="13">
+        <v>5</v>
+      </c>
+      <c r="M27" s="13">
+        <v>6</v>
+      </c>
+      <c r="N27" s="13">
+        <v>6</v>
+      </c>
+      <c r="O27" s="13">
+        <v>7</v>
+      </c>
+      <c r="P27" s="13">
+        <v>7</v>
+      </c>
+      <c r="Q27" s="18">
+        <v>8</v>
+      </c>
+      <c r="R27" s="13">
+        <v>8</v>
+      </c>
+      <c r="S27" s="13">
+        <v>9</v>
+      </c>
+      <c r="T27" s="13">
+        <v>9</v>
+      </c>
+      <c r="U27" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <f t="shared" ref="A28:A30" si="5">A20</f>
+        <v>25</v>
+      </c>
+      <c r="E28" s="13">
         <v>2</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F28" s="13">
         <v>2</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G28" s="13">
         <v>2</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H28" s="13">
         <v>3</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I28" s="13">
         <v>4</v>
       </c>
-      <c r="J18" s="13">
+      <c r="J28" s="13">
         <v>4</v>
       </c>
-      <c r="K18" s="13">
+      <c r="K28" s="13">
         <v>5</v>
       </c>
-      <c r="L18" s="13">
-        <v>5</v>
-      </c>
-      <c r="M18" s="13">
+      <c r="L28" s="13">
         <v>6</v>
       </c>
-      <c r="N18" s="13">
+      <c r="M28" s="13">
         <v>6</v>
       </c>
-      <c r="O18" s="13">
-        <v>7</v>
-      </c>
-      <c r="P18" s="13">
-        <v>7</v>
-      </c>
-      <c r="Q18" s="19">
+      <c r="N28" s="13">
+        <v>6</v>
+      </c>
+      <c r="O28" s="13">
         <v>8</v>
       </c>
-      <c r="R18" s="13">
+      <c r="P28" s="13">
         <v>8</v>
       </c>
-      <c r="S18" s="13">
+      <c r="Q28" s="18">
+        <v>8</v>
+      </c>
+      <c r="R28" s="13">
+        <v>8</v>
+      </c>
+      <c r="S28" s="13">
         <v>9</v>
       </c>
-      <c r="T18" s="13">
-        <v>9</v>
-      </c>
-      <c r="U18" s="13">
+      <c r="T28" s="13">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A19" s="8">
-        <f t="shared" ref="A19:A21" si="5">A11</f>
-        <v>25</v>
-      </c>
-      <c r="E19" s="13">
-        <v>2</v>
-      </c>
-      <c r="F19" s="13">
-        <v>2</v>
-      </c>
-      <c r="G19" s="13">
-        <v>2</v>
-      </c>
-      <c r="H19" s="13">
-        <v>3</v>
-      </c>
-      <c r="I19" s="13">
-        <v>4</v>
-      </c>
-      <c r="J19" s="13">
-        <v>4</v>
-      </c>
-      <c r="K19" s="13">
-        <v>5</v>
-      </c>
-      <c r="L19" s="13">
-        <v>6</v>
-      </c>
-      <c r="M19" s="13">
-        <v>6</v>
-      </c>
-      <c r="N19" s="13">
-        <v>6</v>
-      </c>
-      <c r="O19" s="13">
-        <v>8</v>
-      </c>
-      <c r="P19" s="13">
-        <v>8</v>
-      </c>
-      <c r="Q19" s="19">
-        <v>8</v>
-      </c>
-      <c r="R19" s="13">
-        <v>8</v>
-      </c>
-      <c r="S19" s="13">
-        <v>9</v>
-      </c>
-      <c r="T19" s="13">
+      <c r="U28" s="13">
         <v>10</v>
       </c>
-      <c r="U19" s="13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A20" s="8">
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E29" s="13">
         <v>2</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F29" s="13">
         <v>2</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G29" s="13">
         <v>2</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H29" s="13">
         <v>3</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I29" s="13">
         <v>4</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J29" s="13">
         <v>5</v>
       </c>
-      <c r="K20" s="13">
+      <c r="K29" s="13">
         <v>5</v>
       </c>
-      <c r="L20" s="13">
+      <c r="L29" s="13">
         <v>6</v>
       </c>
-      <c r="M20" s="13">
+      <c r="M29" s="13">
         <v>7</v>
       </c>
-      <c r="N20" s="13">
+      <c r="N29" s="13">
         <v>7</v>
       </c>
-      <c r="O20" s="13">
+      <c r="O29" s="13">
         <v>8</v>
       </c>
-      <c r="P20" s="13">
+      <c r="P29" s="13">
         <v>8</v>
       </c>
-      <c r="Q20" s="19">
+      <c r="Q29" s="18">
         <v>9</v>
       </c>
-      <c r="R20" s="13">
+      <c r="R29" s="13">
         <v>9</v>
       </c>
-      <c r="S20" s="13">
+      <c r="S29" s="13">
         <v>10</v>
       </c>
-      <c r="T20" s="13">
+      <c r="T29" s="13">
         <v>11</v>
       </c>
-      <c r="U20" s="13">
+      <c r="U29" s="13">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A21" s="8">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
         <f t="shared" si="5"/>
         <v>35</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E30" s="13">
         <v>2</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F30" s="13">
         <v>2</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G30" s="13">
         <v>2</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H30" s="13">
         <v>4</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I30" s="13">
         <v>5</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J30" s="13">
         <v>5</v>
       </c>
-      <c r="K21" s="13">
+      <c r="K30" s="13">
         <v>5</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L30" s="13">
         <v>7</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M30" s="13">
         <v>7</v>
       </c>
-      <c r="N21" s="13">
+      <c r="N30" s="13">
         <v>7</v>
       </c>
-      <c r="O21" s="13">
+      <c r="O30" s="13">
         <v>9</v>
       </c>
-      <c r="P21" s="13">
+      <c r="P30" s="13">
         <v>9</v>
       </c>
-      <c r="Q21" s="19">
+      <c r="Q30" s="18">
         <v>10</v>
       </c>
-      <c r="R21" s="13">
+      <c r="R30" s="13">
         <v>10</v>
       </c>
-      <c r="S21" s="13">
+      <c r="S30" s="13">
         <v>10</v>
       </c>
-      <c r="T21" s="13">
+      <c r="T30" s="13">
         <v>11</v>
       </c>
-      <c r="U21" s="13">
+      <c r="U30" s="13">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A22" s="8"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="13"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="13"/>
-      <c r="S22" s="13"/>
-      <c r="T22" s="13"/>
-      <c r="U22" s="13"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="D23" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="13"/>
-      <c r="T23" s="13"/>
-      <c r="U23" s="13"/>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A24" s="25">
-        <f>A17</f>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" s="8"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="18"/>
+      <c r="R31" s="13"/>
+      <c r="S31" s="13"/>
+      <c r="T31" s="13"/>
+      <c r="U31" s="13"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D32" t="str">
+        <f>C11</f>
+        <v xml:space="preserve">Broj koluma blok: </v>
+      </c>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="18"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="13"/>
+      <c r="U32" s="13"/>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33" s="24"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="18"/>
+      <c r="R33" s="13"/>
+      <c r="S33" s="13"/>
+      <c r="T33" s="13"/>
+      <c r="U33" s="13"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <f>A27</f>
+        <v>20</v>
+      </c>
+      <c r="E34" s="13">
+        <v>2</v>
+      </c>
+      <c r="F34" s="13">
+        <v>3</v>
+      </c>
+      <c r="G34" s="13">
+        <v>3</v>
+      </c>
+      <c r="H34" s="13">
+        <v>4</v>
+      </c>
+      <c r="I34" s="13">
+        <v>4</v>
+      </c>
+      <c r="J34" s="13">
+        <v>4</v>
+      </c>
+      <c r="K34" s="13">
+        <v>5</v>
+      </c>
+      <c r="L34" s="13">
+        <v>6</v>
+      </c>
+      <c r="M34" s="13">
+        <v>6</v>
+      </c>
+      <c r="N34" s="13">
+        <v>7</v>
+      </c>
+      <c r="O34" s="13">
+        <v>7</v>
+      </c>
+      <c r="P34" s="13">
+        <v>8</v>
+      </c>
+      <c r="Q34" s="18">
+        <v>8</v>
+      </c>
+      <c r="R34" s="13">
+        <v>9</v>
+      </c>
+      <c r="S34" s="13">
+        <v>9</v>
+      </c>
+      <c r="T34" s="13">
+        <v>10</v>
+      </c>
+      <c r="U34" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
+        <f>A28</f>
+        <v>25</v>
+      </c>
+      <c r="E35" s="13">
+        <v>2</v>
+      </c>
+      <c r="F35" s="13">
+        <v>3</v>
+      </c>
+      <c r="G35" s="13">
+        <v>4</v>
+      </c>
+      <c r="H35" s="13">
+        <v>4</v>
+      </c>
+      <c r="I35" s="13">
+        <v>4</v>
+      </c>
+      <c r="J35" s="13">
+        <v>5</v>
+      </c>
+      <c r="K35" s="13">
+        <v>6</v>
+      </c>
+      <c r="L35" s="13">
+        <v>6</v>
+      </c>
+      <c r="M35" s="13">
+        <v>7</v>
+      </c>
+      <c r="N35" s="13">
+        <v>7</v>
+      </c>
+      <c r="O35" s="13">
+        <v>8</v>
+      </c>
+      <c r="P35" s="13">
+        <v>9</v>
+      </c>
+      <c r="Q35" s="18">
+        <v>9</v>
+      </c>
+      <c r="R35" s="13">
+        <v>9</v>
+      </c>
+      <c r="S35" s="13">
+        <v>10</v>
+      </c>
+      <c r="T35" s="13">
+        <v>10</v>
+      </c>
+      <c r="U35" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
+        <f>A29</f>
+        <v>30</v>
+      </c>
+      <c r="E36" s="13">
+        <v>3</v>
+      </c>
+      <c r="F36" s="13">
+        <v>4</v>
+      </c>
+      <c r="G36" s="13">
+        <v>5</v>
+      </c>
+      <c r="H36" s="13">
+        <v>5</v>
+      </c>
+      <c r="I36" s="13">
+        <v>5</v>
+      </c>
+      <c r="J36" s="13">
+        <v>5</v>
+      </c>
+      <c r="K36" s="13">
+        <v>7</v>
+      </c>
+      <c r="L36" s="13">
+        <v>8</v>
+      </c>
+      <c r="M36" s="13">
+        <v>7</v>
+      </c>
+      <c r="N36" s="13">
+        <v>7</v>
+      </c>
+      <c r="O36" s="13">
+        <v>9</v>
+      </c>
+      <c r="P36" s="13">
+        <v>9</v>
+      </c>
+      <c r="Q36" s="18">
+        <v>9</v>
+      </c>
+      <c r="R36" s="13">
+        <v>9</v>
+      </c>
+      <c r="S36" s="13">
+        <v>10</v>
+      </c>
+      <c r="T36" s="13">
+        <v>11</v>
+      </c>
+      <c r="U36" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
+        <f>A30</f>
         <v>35</v>
       </c>
-      <c r="D24" s="9">
+      <c r="E37" s="13">
         <v>3</v>
       </c>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="13"/>
-      <c r="S24" s="13"/>
-      <c r="T24" s="13"/>
-      <c r="U24" s="13"/>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A25" s="8">
-        <f>A18</f>
+      <c r="F37" s="13">
+        <v>5</v>
+      </c>
+      <c r="G37" s="13">
+        <v>5</v>
+      </c>
+      <c r="H37" s="13">
+        <v>5</v>
+      </c>
+      <c r="I37" s="13">
+        <v>5</v>
+      </c>
+      <c r="J37" s="13">
+        <v>6</v>
+      </c>
+      <c r="K37" s="13">
+        <v>8</v>
+      </c>
+      <c r="L37" s="13">
+        <v>7</v>
+      </c>
+      <c r="M37" s="13">
+        <v>8</v>
+      </c>
+      <c r="N37" s="13">
+        <v>8</v>
+      </c>
+      <c r="O37" s="13">
+        <v>9</v>
+      </c>
+      <c r="P37" s="13">
+        <v>10</v>
+      </c>
+      <c r="Q37" s="18">
+        <v>10</v>
+      </c>
+      <c r="R37" s="13">
+        <v>10</v>
+      </c>
+      <c r="S37" s="13">
+        <v>11</v>
+      </c>
+      <c r="T37" s="13">
+        <v>12</v>
+      </c>
+      <c r="U37" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38" s="8"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
+      <c r="P38" s="13"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="13"/>
+      <c r="S38" s="13"/>
+      <c r="T38" s="13"/>
+      <c r="U38" s="13"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
+      <c r="P39" s="8"/>
+      <c r="Q39" s="19"/>
+      <c r="R39" s="8"/>
+      <c r="S39" s="8"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="8"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40" s="24"/>
+      <c r="D40" t="str">
+        <f>G6</f>
+        <v xml:space="preserve">Težina bloka u kg: </v>
+      </c>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
+      <c r="P40" s="8"/>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="8"/>
+      <c r="S40" s="8"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="8"/>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41" s="8">
+        <f>A34</f>
         <v>20</v>
       </c>
-      <c r="E25" s="13">
-        <v>2</v>
-      </c>
-      <c r="F25" s="13">
-        <v>3</v>
-      </c>
-      <c r="G25" s="13">
-        <v>3</v>
-      </c>
-      <c r="H25" s="13">
-        <v>4</v>
-      </c>
-      <c r="I25" s="13">
-        <v>4</v>
-      </c>
-      <c r="J25" s="13">
-        <v>4</v>
-      </c>
-      <c r="K25" s="13">
-        <v>5</v>
-      </c>
-      <c r="L25" s="13">
-        <v>6</v>
-      </c>
-      <c r="M25" s="13">
-        <v>6</v>
-      </c>
-      <c r="N25" s="13">
-        <v>7</v>
-      </c>
-      <c r="O25" s="13">
-        <v>7</v>
-      </c>
-      <c r="P25" s="13">
-        <v>8</v>
-      </c>
-      <c r="Q25" s="19">
-        <v>8</v>
-      </c>
-      <c r="R25" s="13">
-        <v>9</v>
-      </c>
-      <c r="S25" s="13">
-        <v>9</v>
-      </c>
-      <c r="T25" s="13">
-        <v>10</v>
-      </c>
-      <c r="U25" s="13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A26" s="8">
-        <f>A19</f>
-        <v>25</v>
-      </c>
-      <c r="E26" s="13">
-        <v>2</v>
-      </c>
-      <c r="F26" s="13">
-        <v>3</v>
-      </c>
-      <c r="G26" s="13">
-        <v>4</v>
-      </c>
-      <c r="H26" s="13">
-        <v>4</v>
-      </c>
-      <c r="I26" s="13">
-        <v>4</v>
-      </c>
-      <c r="J26" s="13">
-        <v>5</v>
-      </c>
-      <c r="K26" s="13">
-        <v>6</v>
-      </c>
-      <c r="L26" s="13">
-        <v>6</v>
-      </c>
-      <c r="M26" s="13">
-        <v>7</v>
-      </c>
-      <c r="N26" s="13">
-        <v>7</v>
-      </c>
-      <c r="O26" s="13">
-        <v>8</v>
-      </c>
-      <c r="P26" s="13">
-        <v>9</v>
-      </c>
-      <c r="Q26" s="19">
-        <v>9</v>
-      </c>
-      <c r="R26" s="13">
-        <v>9</v>
-      </c>
-      <c r="S26" s="13">
-        <v>10</v>
-      </c>
-      <c r="T26" s="13">
-        <v>10</v>
-      </c>
-      <c r="U26" s="13">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A27" s="8">
-        <f>A20</f>
-        <v>30</v>
-      </c>
-      <c r="E27" s="13">
-        <v>3</v>
-      </c>
-      <c r="F27" s="13">
-        <v>4</v>
-      </c>
-      <c r="G27" s="13">
-        <v>5</v>
-      </c>
-      <c r="H27" s="13">
-        <v>5</v>
-      </c>
-      <c r="I27" s="13">
-        <v>5</v>
-      </c>
-      <c r="J27" s="13">
-        <v>5</v>
-      </c>
-      <c r="K27" s="13">
-        <v>7</v>
-      </c>
-      <c r="L27" s="13">
-        <v>8</v>
-      </c>
-      <c r="M27" s="13">
-        <v>7</v>
-      </c>
-      <c r="N27" s="13">
-        <v>7</v>
-      </c>
-      <c r="O27" s="13">
-        <v>9</v>
-      </c>
-      <c r="P27" s="13">
-        <v>9</v>
-      </c>
-      <c r="Q27" s="19">
-        <v>9</v>
-      </c>
-      <c r="R27" s="13">
-        <v>9</v>
-      </c>
-      <c r="S27" s="13">
-        <v>10</v>
-      </c>
-      <c r="T27" s="13">
-        <v>11</v>
-      </c>
-      <c r="U27" s="13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A28" s="8">
-        <f>A21</f>
-        <v>35</v>
-      </c>
-      <c r="E28" s="13">
-        <v>3</v>
-      </c>
-      <c r="F28" s="13">
-        <v>5</v>
-      </c>
-      <c r="G28" s="13">
-        <v>5</v>
-      </c>
-      <c r="H28" s="13">
-        <v>5</v>
-      </c>
-      <c r="I28" s="13">
-        <v>5</v>
-      </c>
-      <c r="J28" s="13">
-        <v>6</v>
-      </c>
-      <c r="K28" s="13">
-        <v>8</v>
-      </c>
-      <c r="L28" s="13">
-        <v>7</v>
-      </c>
-      <c r="M28" s="13">
-        <v>8</v>
-      </c>
-      <c r="N28" s="13">
-        <v>8</v>
-      </c>
-      <c r="O28" s="13">
-        <v>9</v>
-      </c>
-      <c r="P28" s="13">
-        <v>10</v>
-      </c>
-      <c r="Q28" s="19">
-        <v>10</v>
-      </c>
-      <c r="R28" s="13">
-        <v>10</v>
-      </c>
-      <c r="S28" s="13">
-        <v>11</v>
-      </c>
-      <c r="T28" s="13">
-        <v>12</v>
-      </c>
-      <c r="U28" s="13">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A29" s="8"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="13"/>
-      <c r="S29" s="13"/>
-      <c r="T29" s="13"/>
-      <c r="U29" s="13"/>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="D30" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="20"/>
-      <c r="R30" s="8"/>
-      <c r="S30" s="8"/>
-      <c r="T30" s="8"/>
-      <c r="U30" s="8"/>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A31" s="25">
-        <f>A24</f>
-        <v>35</v>
-      </c>
-      <c r="D31" s="12">
-        <f>D9/(D17*D24)</f>
-        <v>101.1111111111111</v>
-      </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="8"/>
-      <c r="S31" s="8"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="8"/>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A32" s="8">
-        <f>A25</f>
-        <v>20</v>
-      </c>
-      <c r="E32" s="12">
-        <f t="shared" ref="E32:F35" si="6">E10/(E18*E25)</f>
+      <c r="E41" s="12">
+        <f t="shared" ref="E41:F44" si="6">E19/(E27*E34)</f>
         <v>32.5</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F41" s="12">
         <f t="shared" si="6"/>
         <v>32.5</v>
       </c>
-      <c r="G32" s="12">
-        <f t="shared" ref="G32:U32" si="7">G10/(G18*G25)</f>
+      <c r="G41" s="12">
+        <f t="shared" ref="G41:U41" si="7">G19/(G27*G34)</f>
         <v>43.333333333333336</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H41" s="12">
         <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I41" s="12">
         <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
-      <c r="J32" s="12">
+      <c r="J41" s="12">
         <f t="shared" si="7"/>
         <v>40.625</v>
       </c>
-      <c r="K32" s="12">
+      <c r="K41" s="12">
         <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
-      <c r="L32" s="12">
+      <c r="L41" s="12">
         <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
-      <c r="M32" s="12">
+      <c r="M41" s="12">
         <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
-      <c r="N32" s="12">
+      <c r="N41" s="12">
         <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
-      <c r="O32" s="12">
+      <c r="O41" s="12">
         <f t="shared" si="7"/>
         <v>32.500000000000007</v>
       </c>
-      <c r="P32" s="12">
+      <c r="P41" s="12">
         <f t="shared" si="7"/>
         <v>32.499999999999993</v>
       </c>
-      <c r="Q32" s="21">
+      <c r="Q41" s="20">
         <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
-      <c r="R32" s="12">
+      <c r="R41" s="12">
         <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
-      <c r="S32" s="12">
+      <c r="S41" s="12">
         <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
-      <c r="T32" s="12">
+      <c r="T41" s="12">
         <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
-      <c r="U32" s="12">
+      <c r="U41" s="12">
         <f t="shared" si="7"/>
         <v>32.5</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A33" s="8">
-        <f>A26</f>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42" s="8">
+        <f>A35</f>
         <v>25</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E42" s="12">
         <f t="shared" si="6"/>
         <v>40.625</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F42" s="12">
         <f t="shared" si="6"/>
         <v>40.625</v>
       </c>
-      <c r="G33" s="12">
-        <f t="shared" ref="G33:U33" si="8">G11/(G19*G26)</f>
+      <c r="G42" s="12">
+        <f t="shared" ref="G42:U42" si="8">G20/(G28*G35)</f>
         <v>40.625</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H42" s="12">
         <f t="shared" si="8"/>
         <v>40.625</v>
       </c>
-      <c r="I33" s="12">
+      <c r="I42" s="12">
         <f t="shared" si="8"/>
         <v>40.625</v>
       </c>
-      <c r="J33" s="12">
+      <c r="J42" s="12">
         <f t="shared" si="8"/>
         <v>40.625</v>
       </c>
-      <c r="K33" s="12">
+      <c r="K42" s="12">
         <f t="shared" si="8"/>
         <v>33.854166666666664</v>
       </c>
-      <c r="L33" s="12">
+      <c r="L42" s="12">
         <f t="shared" si="8"/>
         <v>33.854166666666664</v>
       </c>
-      <c r="M33" s="12">
+      <c r="M42" s="12">
         <f t="shared" si="8"/>
         <v>34.821428571428569</v>
       </c>
-      <c r="N33" s="12">
+      <c r="N42" s="12">
         <f t="shared" si="8"/>
         <v>40.625</v>
       </c>
-      <c r="O33" s="12">
+      <c r="O42" s="12">
         <f t="shared" si="8"/>
         <v>31.103515625</v>
       </c>
-      <c r="P33" s="12">
+      <c r="P42" s="12">
         <f t="shared" si="8"/>
         <v>31.597222222222221</v>
       </c>
-      <c r="Q33" s="21">
+      <c r="Q42" s="20">
         <f t="shared" si="8"/>
         <v>36.111111111111114</v>
       </c>
-      <c r="R33" s="12">
+      <c r="R42" s="12">
         <f t="shared" si="8"/>
         <v>40.625</v>
       </c>
-      <c r="S33" s="12">
+      <c r="S42" s="12">
         <f t="shared" si="8"/>
         <v>36.5625</v>
       </c>
-      <c r="T33" s="12">
+      <c r="T42" s="12">
         <f t="shared" si="8"/>
         <v>36.5625</v>
       </c>
-      <c r="U33" s="12">
+      <c r="U42" s="12">
         <f t="shared" si="8"/>
         <v>36.93181818181818</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A34" s="8">
-        <f>A27</f>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43" s="8">
+        <f>A36</f>
         <v>30</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E43" s="12">
         <f t="shared" si="6"/>
         <v>32.5</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F43" s="12">
         <f t="shared" si="6"/>
         <v>36.5625</v>
       </c>
-      <c r="G34" s="12">
-        <f t="shared" ref="G34:T34" si="9">G12/(G20*G27)</f>
+      <c r="G43" s="12">
+        <f t="shared" ref="G43:T43" si="9">G21/(G29*G36)</f>
         <v>39</v>
       </c>
-      <c r="H34" s="12">
+      <c r="H43" s="12">
         <f t="shared" si="9"/>
         <v>39</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I43" s="12">
         <f t="shared" si="9"/>
         <v>39</v>
       </c>
-      <c r="J34" s="12">
+      <c r="J43" s="12">
         <f t="shared" si="9"/>
         <v>39</v>
       </c>
-      <c r="K34" s="12">
+      <c r="K43" s="12">
         <f t="shared" si="9"/>
         <v>34.821428571428569</v>
       </c>
-      <c r="L34" s="12">
+      <c r="L43" s="12">
         <f t="shared" si="9"/>
         <v>30.46875</v>
       </c>
-      <c r="M34" s="12">
+      <c r="M43" s="12">
         <f t="shared" si="9"/>
         <v>35.816326530612251</v>
       </c>
-      <c r="N34" s="12">
+      <c r="N43" s="12">
         <f t="shared" si="9"/>
         <v>41.785714285714285</v>
       </c>
-      <c r="O34" s="12">
+      <c r="O43" s="12">
         <f t="shared" si="9"/>
         <v>33.177083333333336</v>
       </c>
-      <c r="P34" s="12">
+      <c r="P43" s="12">
         <f t="shared" si="9"/>
         <v>37.916666666666664</v>
       </c>
-      <c r="Q34" s="21">
+      <c r="Q43" s="20">
         <f t="shared" si="9"/>
         <v>38.518518518518519</v>
       </c>
-      <c r="R34" s="12">
+      <c r="R43" s="12">
         <f t="shared" si="9"/>
         <v>43.333333333333336</v>
       </c>
-      <c r="S34" s="12">
+      <c r="S43" s="12">
         <f t="shared" si="9"/>
         <v>39.487499999999997</v>
       </c>
-      <c r="T34" s="12">
+      <c r="T43" s="12">
         <f t="shared" si="9"/>
         <v>36.260330578512395</v>
       </c>
-      <c r="U34" s="12">
-        <f t="shared" ref="U34" si="10">U12/(U20*U27)</f>
+      <c r="U43" s="12">
+        <f t="shared" ref="U43" si="10">U21/(U29*U36)</f>
         <v>36.93181818181818</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A35" s="8">
-        <f>A28</f>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A44" s="8">
+        <f>A37</f>
         <v>35</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E44" s="12">
         <f t="shared" si="6"/>
         <v>37.916666666666664</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F44" s="12">
         <f t="shared" si="6"/>
         <v>34.125</v>
       </c>
-      <c r="G35" s="12">
-        <f t="shared" ref="G35:T35" si="11">G13/(G21*G28)</f>
+      <c r="G44" s="12">
+        <f t="shared" ref="G44:T44" si="11">G22/(G30*G37)</f>
         <v>45.499999999999993</v>
       </c>
-      <c r="H35" s="12">
+      <c r="H44" s="12">
         <f t="shared" si="11"/>
         <v>34.125</v>
       </c>
-      <c r="I35" s="12">
+      <c r="I44" s="12">
         <f t="shared" si="11"/>
         <v>36.4</v>
       </c>
-      <c r="J35" s="12">
+      <c r="J44" s="12">
         <f t="shared" si="11"/>
         <v>37.916666666666664</v>
       </c>
-      <c r="K35" s="12">
+      <c r="K44" s="12">
         <f t="shared" si="11"/>
         <v>35.546875</v>
       </c>
-      <c r="L35" s="12">
+      <c r="L44" s="12">
         <f t="shared" si="11"/>
         <v>34.821428571428569</v>
       </c>
-      <c r="M35" s="12">
+      <c r="M44" s="12">
         <f t="shared" si="11"/>
         <v>36.5625</v>
       </c>
-      <c r="N35" s="12">
+      <c r="N44" s="12">
         <f t="shared" si="11"/>
         <v>42.65625</v>
       </c>
-      <c r="O35" s="12">
+      <c r="O44" s="12">
         <f t="shared" si="11"/>
         <v>34.40586419753086</v>
       </c>
-      <c r="P35" s="12">
+      <c r="P44" s="12">
         <f t="shared" si="11"/>
         <v>35.388888888888893</v>
       </c>
-      <c r="Q35" s="21">
+      <c r="Q44" s="20">
         <f t="shared" si="11"/>
         <v>36.4</v>
       </c>
-      <c r="R35" s="12">
+      <c r="R44" s="12">
         <f t="shared" si="11"/>
         <v>40.950000000000003</v>
       </c>
-      <c r="S35" s="12">
+      <c r="S44" s="12">
         <f t="shared" si="11"/>
         <v>41.88068181818182</v>
       </c>
-      <c r="T35" s="12">
+      <c r="T44" s="12">
         <f t="shared" si="11"/>
         <v>38.778409090909093</v>
       </c>
-      <c r="U35" s="12">
-        <f t="shared" ref="U35" si="12">U13/(U21*U28)</f>
+      <c r="U44" s="12">
+        <f t="shared" ref="U44" si="12">U22/(U30*U37)</f>
         <v>36.458333333333336</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="D37" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A38" s="25">
-        <f>A31</f>
-        <v>35</v>
-      </c>
-      <c r="D38" s="12">
-        <f>(D17+1)*2+(D24-1)*2</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A39" s="8">
-        <f>A32</f>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A47" s="24"/>
+      <c r="D47" t="str">
+        <f>G7</f>
+        <v>Broj rupa kod rastera :</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A48" s="8">
+        <f>A41</f>
         <v>20</v>
       </c>
-      <c r="E39" s="12">
-        <f>(E18+1)*2+(E25-1)*2</f>
+      <c r="E48" s="12">
+        <f>(E27+1)*2+(E34-1)*2</f>
         <v>8</v>
       </c>
-      <c r="F39" s="12">
-        <f t="shared" ref="F39:U39" si="13">(F18+1)*2+(F25-1)*2</f>
+      <c r="F48" s="12">
+        <f t="shared" ref="F48:U48" si="13">(F27+1)*2+(F34-1)*2</f>
         <v>10</v>
       </c>
-      <c r="G39" s="12">
+      <c r="G48" s="12">
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
-      <c r="H39" s="12">
+      <c r="H48" s="12">
         <f t="shared" si="13"/>
         <v>14</v>
       </c>
-      <c r="I39" s="12">
+      <c r="I48" s="12">
         <f t="shared" si="13"/>
         <v>16</v>
       </c>
-      <c r="J39" s="12">
+      <c r="J48" s="12">
         <f t="shared" si="13"/>
         <v>16</v>
       </c>
-      <c r="K39" s="12">
+      <c r="K48" s="12">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
-      <c r="L39" s="12">
+      <c r="L48" s="12">
         <f t="shared" si="13"/>
         <v>22</v>
       </c>
-      <c r="M39" s="12">
+      <c r="M48" s="12">
         <f t="shared" si="13"/>
         <v>24</v>
       </c>
-      <c r="N39" s="12">
+      <c r="N48" s="12">
         <f t="shared" si="13"/>
         <v>26</v>
       </c>
-      <c r="O39" s="12">
+      <c r="O48" s="12">
         <f t="shared" si="13"/>
         <v>28</v>
       </c>
-      <c r="P39" s="12">
+      <c r="P48" s="12">
         <f t="shared" si="13"/>
         <v>30</v>
       </c>
-      <c r="Q39" s="21">
+      <c r="Q48" s="20">
         <f t="shared" si="13"/>
         <v>32</v>
       </c>
-      <c r="R39" s="12">
+      <c r="R48" s="12">
         <f t="shared" si="13"/>
         <v>34</v>
       </c>
-      <c r="S39" s="12">
+      <c r="S48" s="12">
         <f t="shared" si="13"/>
         <v>36</v>
       </c>
-      <c r="T39" s="12">
+      <c r="T48" s="12">
         <f t="shared" si="13"/>
         <v>38</v>
       </c>
-      <c r="U39" s="12">
+      <c r="U48" s="12">
         <f t="shared" si="13"/>
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A40" s="8">
-        <f t="shared" ref="A40:A42" si="14">A33</f>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A49" s="8">
+        <f t="shared" ref="A49:A51" si="14">A42</f>
         <v>25</v>
       </c>
-      <c r="E40" s="12">
-        <f>(E19+1)*2+(E26-1)*2</f>
+      <c r="E49" s="12">
+        <f>(E28+1)*2+(E35-1)*2</f>
         <v>8</v>
       </c>
-      <c r="F40" s="12">
-        <f t="shared" ref="F40:U40" si="15">(F19+1)*2+(F26-1)*2</f>
+      <c r="F49" s="12">
+        <f t="shared" ref="F49:U49" si="15">(F28+1)*2+(F35-1)*2</f>
         <v>10</v>
       </c>
-      <c r="G40" s="12">
+      <c r="G49" s="12">
         <f t="shared" si="15"/>
         <v>12</v>
       </c>
-      <c r="H40" s="12">
+      <c r="H49" s="12">
         <f t="shared" si="15"/>
         <v>14</v>
       </c>
-      <c r="I40" s="12">
+      <c r="I49" s="12">
         <f t="shared" si="15"/>
         <v>16</v>
       </c>
-      <c r="J40" s="12">
+      <c r="J49" s="12">
         <f t="shared" si="15"/>
         <v>18</v>
       </c>
-      <c r="K40" s="12">
+      <c r="K49" s="12">
         <f t="shared" si="15"/>
         <v>22</v>
       </c>
-      <c r="L40" s="12">
+      <c r="L49" s="12">
         <f t="shared" si="15"/>
         <v>24</v>
       </c>
-      <c r="M40" s="12">
+      <c r="M49" s="12">
         <f t="shared" si="15"/>
         <v>26</v>
       </c>
-      <c r="N40" s="12">
+      <c r="N49" s="12">
         <f t="shared" si="15"/>
         <v>26</v>
       </c>
-      <c r="O40" s="12">
+      <c r="O49" s="12">
         <f t="shared" si="15"/>
         <v>32</v>
       </c>
-      <c r="P40" s="12">
+      <c r="P49" s="12">
         <f t="shared" si="15"/>
         <v>34</v>
       </c>
-      <c r="Q40" s="21">
+      <c r="Q49" s="20">
         <f t="shared" si="15"/>
         <v>34</v>
       </c>
-      <c r="R40" s="12">
+      <c r="R49" s="12">
         <f t="shared" si="15"/>
         <v>34</v>
       </c>
-      <c r="S40" s="12">
+      <c r="S49" s="12">
         <f t="shared" si="15"/>
         <v>38</v>
       </c>
-      <c r="T40" s="12">
+      <c r="T49" s="12">
         <f t="shared" si="15"/>
         <v>40</v>
       </c>
-      <c r="U40" s="12">
+      <c r="U49" s="12">
         <f t="shared" si="15"/>
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A41" s="8">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A50" s="8">
         <f t="shared" si="14"/>
         <v>30</v>
       </c>
-      <c r="E41" s="12">
-        <f>(E20+1)*2+(E27-1)*2</f>
+      <c r="E50" s="12">
+        <f>(E29+1)*2+(E36-1)*2</f>
         <v>10</v>
       </c>
-      <c r="F41" s="12">
-        <f t="shared" ref="F41:U41" si="16">(F20+1)*2+(F27-1)*2</f>
+      <c r="F50" s="12">
+        <f t="shared" ref="F50:U50" si="16">(F29+1)*2+(F36-1)*2</f>
         <v>12</v>
       </c>
-      <c r="G41" s="12">
+      <c r="G50" s="12">
         <f t="shared" si="16"/>
         <v>14</v>
       </c>
-      <c r="H41" s="12">
+      <c r="H50" s="12">
         <f t="shared" si="16"/>
         <v>16</v>
       </c>
-      <c r="I41" s="12">
+      <c r="I50" s="12">
         <f t="shared" si="16"/>
         <v>18</v>
       </c>
-      <c r="J41" s="12">
+      <c r="J50" s="12">
         <f t="shared" si="16"/>
         <v>20</v>
       </c>
-      <c r="K41" s="12">
+      <c r="K50" s="12">
         <f t="shared" si="16"/>
         <v>24</v>
       </c>
-      <c r="L41" s="12">
+      <c r="L50" s="12">
         <f t="shared" si="16"/>
         <v>28</v>
       </c>
-      <c r="M41" s="12">
+      <c r="M50" s="12">
         <f t="shared" si="16"/>
         <v>28</v>
       </c>
-      <c r="N41" s="12">
+      <c r="N50" s="12">
         <f t="shared" si="16"/>
         <v>28</v>
       </c>
-      <c r="O41" s="12">
+      <c r="O50" s="12">
         <f t="shared" si="16"/>
         <v>34</v>
       </c>
-      <c r="P41" s="12">
+      <c r="P50" s="12">
         <f t="shared" si="16"/>
         <v>34</v>
       </c>
-      <c r="Q41" s="21">
+      <c r="Q50" s="20">
         <f t="shared" si="16"/>
         <v>36</v>
       </c>
-      <c r="R41" s="12">
+      <c r="R50" s="12">
         <f t="shared" si="16"/>
         <v>36</v>
       </c>
-      <c r="S41" s="12">
+      <c r="S50" s="12">
         <f t="shared" si="16"/>
         <v>40</v>
       </c>
-      <c r="T41" s="12">
+      <c r="T50" s="12">
         <f t="shared" si="16"/>
         <v>44</v>
       </c>
-      <c r="U41" s="12">
+      <c r="U50" s="12">
         <f t="shared" si="16"/>
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A42" s="8">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A51" s="8">
         <f t="shared" si="14"/>
         <v>35</v>
       </c>
-      <c r="E42" s="12">
-        <f>(E21+1)*2+(E28-1)*2</f>
+      <c r="E51" s="12">
+        <f>(E30+1)*2+(E37-1)*2</f>
         <v>10</v>
       </c>
-      <c r="F42" s="12">
-        <f t="shared" ref="F42:U42" si="17">(F21+1)*2+(F28-1)*2</f>
+      <c r="F51" s="12">
+        <f t="shared" ref="F51:U51" si="17">(F30+1)*2+(F37-1)*2</f>
         <v>14</v>
       </c>
-      <c r="G42" s="12">
+      <c r="G51" s="12">
         <f t="shared" si="17"/>
         <v>14</v>
       </c>
-      <c r="H42" s="12">
+      <c r="H51" s="12">
         <f t="shared" si="17"/>
         <v>18</v>
       </c>
-      <c r="I42" s="12">
+      <c r="I51" s="12">
         <f t="shared" si="17"/>
         <v>20</v>
       </c>
-      <c r="J42" s="12">
+      <c r="J51" s="12">
         <f t="shared" si="17"/>
         <v>22</v>
       </c>
-      <c r="K42" s="12">
+      <c r="K51" s="12">
         <f t="shared" si="17"/>
         <v>26</v>
       </c>
-      <c r="L42" s="12">
+      <c r="L51" s="12">
         <f t="shared" si="17"/>
         <v>28</v>
       </c>
-      <c r="M42" s="12">
+      <c r="M51" s="12">
         <f t="shared" si="17"/>
         <v>30</v>
       </c>
-      <c r="N42" s="12">
+      <c r="N51" s="12">
         <f t="shared" si="17"/>
         <v>30</v>
       </c>
-      <c r="O42" s="12">
+      <c r="O51" s="12">
         <f t="shared" si="17"/>
         <v>36</v>
       </c>
-      <c r="P42" s="12">
+      <c r="P51" s="12">
         <f t="shared" si="17"/>
         <v>38</v>
       </c>
-      <c r="Q42" s="21">
+      <c r="Q51" s="20">
         <f t="shared" si="17"/>
         <v>40</v>
       </c>
-      <c r="R42" s="12">
+      <c r="R51" s="12">
         <f t="shared" si="17"/>
         <v>40</v>
       </c>
-      <c r="S42" s="12">
+      <c r="S51" s="12">
         <f t="shared" si="17"/>
         <v>42</v>
       </c>
-      <c r="T42" s="12">
+      <c r="T51" s="12">
         <f t="shared" si="17"/>
         <v>46</v>
       </c>
-      <c r="U42" s="12">
+      <c r="U51" s="12">
         <f t="shared" si="17"/>
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="D44" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A45" s="25">
-        <f>A17</f>
-        <v>35</v>
-      </c>
-      <c r="D45" s="4">
-        <f>$P$2*$A$45*((D17+1)*D5+(D24+1)*D6)</f>
-        <v>840</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A46" s="8">
-        <f>A39</f>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D53" t="str">
+        <f>G9</f>
+        <v xml:space="preserve">Cijena rezanja: </v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A54" s="24">
+        <f>A26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A55" s="8">
+        <f>A48</f>
         <v>20</v>
       </c>
-      <c r="E46" s="4">
-        <f>$P$2*$A$46*((E18+1)*E5+(E25+1)*E6)</f>
-        <v>180</v>
-      </c>
-      <c r="F46" s="4">
-        <f t="shared" ref="F46:U46" si="18">$P$2*$A$46*((F18+1)*F5+(F25+1)*F6)</f>
-        <v>270</v>
-      </c>
-      <c r="G46" s="4">
+      <c r="E55" s="4">
+        <f>$P$2*$A$55*((E27+1)*E14+(E34+1)*E15)</f>
+        <v>132</v>
+      </c>
+      <c r="F55" s="4">
+        <f t="shared" ref="F55:U55" si="18">$P$2*$A$55*((F27+1)*F14+(F34+1)*F15)</f>
+        <v>198</v>
+      </c>
+      <c r="G55" s="4">
         <f t="shared" si="18"/>
-        <v>330</v>
-      </c>
-      <c r="H46" s="4">
+        <v>242</v>
+      </c>
+      <c r="H55" s="4">
         <f t="shared" si="18"/>
-        <v>480</v>
-      </c>
-      <c r="I46" s="4">
+        <v>352</v>
+      </c>
+      <c r="I55" s="4">
         <f t="shared" si="18"/>
-        <v>600</v>
-      </c>
-      <c r="J46" s="4">
+        <v>440</v>
+      </c>
+      <c r="J55" s="4">
         <f t="shared" si="18"/>
-        <v>675</v>
-      </c>
-      <c r="K46" s="4">
+        <v>495</v>
+      </c>
+      <c r="K55" s="4">
         <f t="shared" si="18"/>
-        <v>900</v>
-      </c>
-      <c r="L46" s="4">
+        <v>660</v>
+      </c>
+      <c r="L55" s="4">
         <f t="shared" si="18"/>
-        <v>1080</v>
-      </c>
-      <c r="M46" s="4">
+        <v>792</v>
+      </c>
+      <c r="M55" s="4">
         <f t="shared" si="18"/>
-        <v>1260</v>
-      </c>
-      <c r="N46" s="4">
+        <v>924</v>
+      </c>
+      <c r="N55" s="4">
         <f t="shared" si="18"/>
-        <v>1470</v>
-      </c>
-      <c r="O46" s="4">
+        <v>1078</v>
+      </c>
+      <c r="O55" s="4">
         <f t="shared" si="18"/>
-        <v>1680</v>
-      </c>
-      <c r="P46" s="4">
+        <v>1232</v>
+      </c>
+      <c r="P55" s="4">
         <f t="shared" si="18"/>
-        <v>1920</v>
-      </c>
-      <c r="Q46" s="4">
+        <v>1408</v>
+      </c>
+      <c r="Q55" s="4">
         <f t="shared" si="18"/>
-        <v>2160</v>
-      </c>
-      <c r="R46" s="4">
+        <v>1584</v>
+      </c>
+      <c r="R55" s="4">
         <f t="shared" si="18"/>
-        <v>2430</v>
-      </c>
-      <c r="S46" s="4">
+        <v>1782</v>
+      </c>
+      <c r="S55" s="4">
         <f t="shared" si="18"/>
-        <v>2700</v>
-      </c>
-      <c r="T46" s="4">
+        <v>1980</v>
+      </c>
+      <c r="T55" s="4">
         <f t="shared" si="18"/>
-        <v>3000</v>
-      </c>
-      <c r="U46" s="4">
+        <v>2200</v>
+      </c>
+      <c r="U55" s="4">
         <f t="shared" si="18"/>
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A47" s="8">
-        <f t="shared" ref="A47:A49" si="19">A40</f>
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A56" s="8">
+        <f t="shared" ref="A56:A58" si="19">A49</f>
         <v>25</v>
       </c>
-      <c r="E47" s="4">
-        <f>$P$2*$A$47*((E19+1)*E5+(E26+1)*E6)</f>
-        <v>225</v>
-      </c>
-      <c r="F47" s="4">
-        <f t="shared" ref="F47:U47" si="20">$P$2*$A$47*((F19+1)*F5+(F26+1)*F6)</f>
-        <v>337.5</v>
-      </c>
-      <c r="G47" s="4">
+      <c r="E56" s="4">
+        <f>$P$2*$A$56*((E28+1)*E14+(E35+1)*E15)</f>
+        <v>165.00000000000003</v>
+      </c>
+      <c r="F56" s="4">
+        <f t="shared" ref="F56:U56" si="20">$P$2*$A$56*((F28+1)*F14+(F35+1)*F15)</f>
+        <v>247.50000000000003</v>
+      </c>
+      <c r="G56" s="4">
         <f t="shared" si="20"/>
-        <v>487.5</v>
-      </c>
-      <c r="H47" s="4">
+        <v>357.50000000000006</v>
+      </c>
+      <c r="H56" s="4">
         <f t="shared" si="20"/>
-        <v>600</v>
-      </c>
-      <c r="I47" s="4">
+        <v>440.00000000000006</v>
+      </c>
+      <c r="I56" s="4">
         <f t="shared" si="20"/>
-        <v>750</v>
-      </c>
-      <c r="J47" s="4">
+        <v>550.00000000000011</v>
+      </c>
+      <c r="J56" s="4">
         <f t="shared" si="20"/>
-        <v>937.5</v>
-      </c>
-      <c r="K47" s="4">
+        <v>687.50000000000011</v>
+      </c>
+      <c r="K56" s="4">
         <f t="shared" si="20"/>
-        <v>1218.75</v>
-      </c>
-      <c r="L47" s="4">
+        <v>893.75000000000011</v>
+      </c>
+      <c r="L56" s="4">
         <f t="shared" si="20"/>
-        <v>1443.75</v>
-      </c>
-      <c r="M47" s="4">
+        <v>1058.7500000000002</v>
+      </c>
+      <c r="M56" s="4">
         <f t="shared" si="20"/>
-        <v>1687.5</v>
-      </c>
-      <c r="N47" s="4">
+        <v>1237.5000000000002</v>
+      </c>
+      <c r="N56" s="4">
         <f t="shared" si="20"/>
-        <v>1837.5</v>
-      </c>
-      <c r="O47" s="4">
+        <v>1347.5000000000002</v>
+      </c>
+      <c r="O56" s="4">
         <f t="shared" si="20"/>
-        <v>2362.5</v>
-      </c>
-      <c r="P47" s="4">
+        <v>1732.5000000000002</v>
+      </c>
+      <c r="P56" s="4">
         <f t="shared" si="20"/>
-        <v>2681.25</v>
-      </c>
-      <c r="Q47" s="4">
+        <v>1966.2500000000002</v>
+      </c>
+      <c r="Q56" s="4">
         <f t="shared" si="20"/>
-        <v>2850</v>
-      </c>
-      <c r="R47" s="4">
+        <v>2090.0000000000005</v>
+      </c>
+      <c r="R56" s="4">
         <f t="shared" si="20"/>
-        <v>3037.5</v>
-      </c>
-      <c r="S47" s="4">
+        <v>2227.5000000000005</v>
+      </c>
+      <c r="S56" s="4">
         <f t="shared" si="20"/>
-        <v>3543.75</v>
-      </c>
-      <c r="T47" s="4">
+        <v>2598.7500000000005</v>
+      </c>
+      <c r="T56" s="4">
         <f t="shared" si="20"/>
-        <v>3918.75</v>
-      </c>
-      <c r="U47" s="4">
+        <v>2873.7500000000005</v>
+      </c>
+      <c r="U56" s="4">
         <f t="shared" si="20"/>
-        <v>4312.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A48" s="8">
+        <v>3162.5000000000005</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A57" s="8">
         <f t="shared" si="19"/>
         <v>30</v>
       </c>
-      <c r="E48" s="4">
-        <f>$P$2*$A$48*((E20+1)*E5+(E27+1)*E6)</f>
-        <v>315</v>
-      </c>
-      <c r="F48" s="4">
-        <f t="shared" ref="F48:U48" si="21">$P$2*$A$48*((F20+1)*F5+(F27+1)*F6)</f>
-        <v>472.5</v>
-      </c>
-      <c r="G48" s="4">
+      <c r="E57" s="4">
+        <f>$P$2*$A$57*((E29+1)*E14+(E36+1)*E15)</f>
+        <v>231</v>
+      </c>
+      <c r="F57" s="4">
+        <f t="shared" ref="F57:U57" si="21">$P$2*$A$57*((F29+1)*F14+(F36+1)*F15)</f>
+        <v>346.5</v>
+      </c>
+      <c r="G57" s="4">
         <f t="shared" si="21"/>
-        <v>675</v>
-      </c>
-      <c r="H48" s="4">
+        <v>495</v>
+      </c>
+      <c r="H57" s="4">
         <f t="shared" si="21"/>
-        <v>810</v>
-      </c>
-      <c r="I48" s="4">
+        <v>594</v>
+      </c>
+      <c r="I57" s="4">
         <f t="shared" si="21"/>
-        <v>990</v>
-      </c>
-      <c r="J48" s="4">
+        <v>726</v>
+      </c>
+      <c r="J57" s="4">
         <f t="shared" si="21"/>
-        <v>1215</v>
-      </c>
-      <c r="K48" s="4">
+        <v>891</v>
+      </c>
+      <c r="K57" s="4">
         <f t="shared" si="21"/>
-        <v>1575</v>
-      </c>
-      <c r="L48" s="4">
+        <v>1155</v>
+      </c>
+      <c r="L57" s="4">
         <f t="shared" si="21"/>
-        <v>2002.5</v>
-      </c>
-      <c r="M48" s="4">
+        <v>1468.5</v>
+      </c>
+      <c r="M57" s="4">
         <f t="shared" si="21"/>
-        <v>2160</v>
-      </c>
-      <c r="N48" s="4">
+        <v>1584</v>
+      </c>
+      <c r="N57" s="4">
         <f t="shared" si="21"/>
-        <v>2340</v>
-      </c>
-      <c r="O48" s="4">
+        <v>1716</v>
+      </c>
+      <c r="O57" s="4">
         <f t="shared" si="21"/>
-        <v>2992.5</v>
-      </c>
-      <c r="P48" s="4">
+        <v>2194.5</v>
+      </c>
+      <c r="P57" s="4">
         <f t="shared" si="21"/>
-        <v>3217.5</v>
-      </c>
-      <c r="Q48" s="4">
+        <v>2359.5</v>
+      </c>
+      <c r="Q57" s="4">
         <f t="shared" si="21"/>
-        <v>3600</v>
-      </c>
-      <c r="R48" s="4">
+        <v>2640</v>
+      </c>
+      <c r="R57" s="4">
         <f t="shared" si="21"/>
-        <v>3825</v>
-      </c>
-      <c r="S48" s="4">
+        <v>2805</v>
+      </c>
+      <c r="S57" s="4">
         <f t="shared" si="21"/>
-        <v>4455</v>
-      </c>
-      <c r="T48" s="4">
+        <v>3267</v>
+      </c>
+      <c r="T57" s="4">
         <f t="shared" si="21"/>
-        <v>5130</v>
-      </c>
-      <c r="U48" s="4">
+        <v>3762</v>
+      </c>
+      <c r="U57" s="4">
         <f t="shared" si="21"/>
-        <v>5625</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A49" s="8">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A58" s="8">
         <f t="shared" si="19"/>
         <v>35</v>
       </c>
-      <c r="E49" s="4">
-        <f>$P$2*$A$49*((E21+1)*E5+(E28+1)*E6)</f>
-        <v>367.5</v>
-      </c>
-      <c r="F49" s="4">
-        <f t="shared" ref="F49:U49" si="22">$P$2*$A$49*((F21+1)*F5+(F28+1)*F6)</f>
-        <v>630</v>
-      </c>
-      <c r="G49" s="4">
+      <c r="E58" s="4">
+        <f>$P$2*$A$58*((E30+1)*E14+(E37+1)*E15)</f>
+        <v>269.5</v>
+      </c>
+      <c r="F58" s="4">
+        <f t="shared" ref="F58:U58" si="22">$P$2*$A$58*((F30+1)*F14+(F37+1)*F15)</f>
+        <v>462</v>
+      </c>
+      <c r="G58" s="4">
         <f t="shared" si="22"/>
-        <v>787.5</v>
-      </c>
-      <c r="H49" s="4">
+        <v>577.5</v>
+      </c>
+      <c r="H58" s="4">
         <f t="shared" si="22"/>
-        <v>1023.75</v>
-      </c>
-      <c r="I49" s="4">
+        <v>750.75</v>
+      </c>
+      <c r="I58" s="4">
         <f t="shared" si="22"/>
-        <v>1260</v>
-      </c>
-      <c r="J49" s="4">
+        <v>924</v>
+      </c>
+      <c r="J58" s="4">
         <f t="shared" si="22"/>
-        <v>1548.75</v>
-      </c>
-      <c r="K49" s="4">
+        <v>1135.75</v>
+      </c>
+      <c r="K58" s="4">
         <f t="shared" si="22"/>
-        <v>1968.75</v>
-      </c>
-      <c r="L49" s="4">
+        <v>1443.75</v>
+      </c>
+      <c r="L58" s="4">
         <f t="shared" si="22"/>
-        <v>2310</v>
-      </c>
-      <c r="M49" s="4">
+        <v>1694</v>
+      </c>
+      <c r="M58" s="4">
         <f t="shared" si="22"/>
-        <v>2677.5</v>
-      </c>
-      <c r="N49" s="4">
+        <v>1963.5</v>
+      </c>
+      <c r="N58" s="4">
         <f t="shared" si="22"/>
-        <v>2913.75</v>
-      </c>
-      <c r="O49" s="4">
+        <v>2136.75</v>
+      </c>
+      <c r="O58" s="4">
         <f t="shared" si="22"/>
-        <v>3675</v>
-      </c>
-      <c r="P49" s="4">
+        <v>2695</v>
+      </c>
+      <c r="P58" s="4">
         <f t="shared" si="22"/>
-        <v>4147.5</v>
-      </c>
-      <c r="Q49" s="4">
+        <v>3041.5</v>
+      </c>
+      <c r="Q58" s="4">
         <f t="shared" si="22"/>
-        <v>4620</v>
-      </c>
-      <c r="R49" s="4">
+        <v>3388</v>
+      </c>
+      <c r="R58" s="4">
         <f t="shared" si="22"/>
-        <v>4908.75</v>
-      </c>
-      <c r="S49" s="4">
+        <v>3599.75</v>
+      </c>
+      <c r="S58" s="4">
         <f t="shared" si="22"/>
-        <v>5433.75</v>
-      </c>
-      <c r="T49" s="4">
+        <v>3984.75</v>
+      </c>
+      <c r="T58" s="4">
         <f t="shared" si="22"/>
-        <v>6247.5</v>
-      </c>
-      <c r="U49" s="4">
+        <v>4581.5</v>
+      </c>
+      <c r="U58" s="4">
         <f t="shared" si="22"/>
-        <v>7087.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A52" s="10">
-        <f>A45</f>
-        <v>35</v>
-      </c>
-      <c r="D52" s="15">
-        <f>$A$53*D38*$L$2*$L$3/100</f>
-        <v>749.76</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A53" s="8">
-        <f>A46</f>
+        <v>5197.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D60" t="str">
+        <f>G11</f>
+        <v xml:space="preserve">Cijena rupa: </v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A61" s="10">
+        <f>A54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A62" s="8">
+        <f>A55</f>
         <v>20</v>
       </c>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15">
-        <f>$A$53*E39*$L$2*$L$3/100</f>
-        <v>499.84</v>
-      </c>
-      <c r="F53" s="15">
-        <f t="shared" ref="F53:T53" si="23">$A$53*F39*$L$2*$L$3/100</f>
-        <v>624.80000000000007</v>
-      </c>
-      <c r="G53" s="15">
+      <c r="D62" s="14"/>
+      <c r="E62" s="14">
+        <f>$A$62*E48*$L$2*$L$3/100</f>
+        <v>359.04</v>
+      </c>
+      <c r="F62" s="14">
+        <f t="shared" ref="F62:T62" si="23">$A$62*F48*$L$2*$L$3/100</f>
+        <v>448.80000000000007</v>
+      </c>
+      <c r="G62" s="14">
         <f t="shared" si="23"/>
-        <v>624.80000000000007</v>
-      </c>
-      <c r="H53" s="15">
+        <v>448.80000000000007</v>
+      </c>
+      <c r="H62" s="14">
         <f t="shared" si="23"/>
-        <v>874.72</v>
-      </c>
-      <c r="I53" s="15">
+        <v>628.32000000000005</v>
+      </c>
+      <c r="I62" s="14">
         <f t="shared" si="23"/>
-        <v>999.68</v>
-      </c>
-      <c r="J53" s="15">
+        <v>718.08</v>
+      </c>
+      <c r="J62" s="14">
         <f t="shared" si="23"/>
-        <v>999.68</v>
-      </c>
-      <c r="K53" s="15">
+        <v>718.08</v>
+      </c>
+      <c r="K62" s="14">
         <f t="shared" si="23"/>
-        <v>1249.6000000000001</v>
-      </c>
-      <c r="L53" s="15">
+        <v>897.60000000000014</v>
+      </c>
+      <c r="L62" s="14">
         <f t="shared" si="23"/>
-        <v>1374.5600000000004</v>
-      </c>
-      <c r="M53" s="15">
+        <v>987.36000000000013</v>
+      </c>
+      <c r="M62" s="14">
         <f t="shared" si="23"/>
-        <v>1499.52</v>
-      </c>
-      <c r="N53" s="15">
+        <v>1077.1199999999999</v>
+      </c>
+      <c r="N62" s="14">
         <f t="shared" si="23"/>
-        <v>1624.48</v>
-      </c>
-      <c r="O53" s="15">
+        <v>1166.8800000000001</v>
+      </c>
+      <c r="O62" s="14">
         <f t="shared" si="23"/>
-        <v>1749.44</v>
-      </c>
-      <c r="P53" s="15">
+        <v>1256.6400000000001</v>
+      </c>
+      <c r="P62" s="14">
         <f t="shared" si="23"/>
-        <v>1874.4</v>
-      </c>
-      <c r="Q53" s="22">
+        <v>1346.4</v>
+      </c>
+      <c r="Q62" s="21">
         <f t="shared" si="23"/>
-        <v>1999.36</v>
-      </c>
-      <c r="R53" s="15">
+        <v>1436.16</v>
+      </c>
+      <c r="R62" s="14">
         <f t="shared" si="23"/>
-        <v>2124.3200000000002</v>
-      </c>
-      <c r="S53" s="15">
+        <v>1525.9200000000003</v>
+      </c>
+      <c r="S62" s="14">
         <f t="shared" si="23"/>
-        <v>2249.2800000000002</v>
-      </c>
-      <c r="T53" s="15">
+        <v>1615.6800000000003</v>
+      </c>
+      <c r="T62" s="14">
         <f t="shared" si="23"/>
-        <v>2374.2400000000002</v>
-      </c>
-      <c r="U53" s="15">
-        <f>$A$53*U39*$L$2*$L$3/100</f>
-        <v>2499.2000000000003</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A54" s="8">
-        <f t="shared" ref="A54:A56" si="24">A47</f>
+        <v>1705.4400000000003</v>
+      </c>
+      <c r="U62" s="14">
+        <f>$A$62*U48*$L$2*$L$3/100</f>
+        <v>1795.2000000000003</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A63" s="8">
+        <f t="shared" ref="A63:A65" si="24">A56</f>
         <v>25</v>
       </c>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15">
-        <f>$A$54*E40*$L$2*$L$3/100</f>
-        <v>624.80000000000007</v>
-      </c>
-      <c r="F54" s="15">
-        <f t="shared" ref="F54:U54" si="25">$A$54*F40*$L$2*$L$3/100</f>
-        <v>781</v>
-      </c>
-      <c r="G54" s="15">
+      <c r="D63" s="14"/>
+      <c r="E63" s="14">
+        <f>$A$63*E49*$L$2*$L$3/100</f>
+        <v>448.80000000000007</v>
+      </c>
+      <c r="F63" s="14">
+        <f t="shared" ref="F63:U63" si="25">$A$63*F49*$L$2*$L$3/100</f>
+        <v>561</v>
+      </c>
+      <c r="G63" s="14">
         <f t="shared" si="25"/>
-        <v>937.2</v>
-      </c>
-      <c r="H54" s="15">
+        <v>673.2</v>
+      </c>
+      <c r="H63" s="14">
         <f t="shared" si="25"/>
-        <v>1093.4000000000001</v>
-      </c>
-      <c r="I54" s="15">
+        <v>785.40000000000009</v>
+      </c>
+      <c r="I63" s="14">
         <f t="shared" si="25"/>
-        <v>1249.6000000000001</v>
-      </c>
-      <c r="J54" s="15">
+        <v>897.60000000000014</v>
+      </c>
+      <c r="J63" s="14">
         <f t="shared" si="25"/>
-        <v>1405.8000000000002</v>
-      </c>
-      <c r="K54" s="15">
+        <v>1009.8000000000002</v>
+      </c>
+      <c r="K63" s="14">
         <f t="shared" si="25"/>
-        <v>1718.2</v>
-      </c>
-      <c r="L54" s="15">
+        <v>1234.2</v>
+      </c>
+      <c r="L63" s="14">
         <f t="shared" si="25"/>
-        <v>1874.4</v>
-      </c>
-      <c r="M54" s="15">
+        <v>1346.4</v>
+      </c>
+      <c r="M63" s="14">
         <f t="shared" si="25"/>
-        <v>2030.6000000000004</v>
-      </c>
-      <c r="N54" s="15">
+        <v>1458.6000000000004</v>
+      </c>
+      <c r="N63" s="14">
         <f t="shared" si="25"/>
-        <v>2030.6000000000004</v>
-      </c>
-      <c r="O54" s="15">
+        <v>1458.6000000000004</v>
+      </c>
+      <c r="O63" s="14">
         <f t="shared" si="25"/>
-        <v>2499.2000000000003</v>
-      </c>
-      <c r="P54" s="15">
+        <v>1795.2000000000003</v>
+      </c>
+      <c r="P63" s="14">
         <f t="shared" si="25"/>
-        <v>2655.4000000000005</v>
-      </c>
-      <c r="Q54" s="22">
+        <v>1907.4000000000003</v>
+      </c>
+      <c r="Q63" s="21">
         <f t="shared" si="25"/>
-        <v>2655.4000000000005</v>
-      </c>
-      <c r="R54" s="15">
+        <v>1907.4000000000003</v>
+      </c>
+      <c r="R63" s="14">
         <f t="shared" si="25"/>
-        <v>2655.4000000000005</v>
-      </c>
-      <c r="S54" s="15">
+        <v>1907.4000000000003</v>
+      </c>
+      <c r="S63" s="14">
         <f t="shared" si="25"/>
-        <v>2967.8</v>
-      </c>
-      <c r="T54" s="15">
+        <v>2131.8000000000002</v>
+      </c>
+      <c r="T63" s="14">
         <f t="shared" si="25"/>
-        <v>3124</v>
-      </c>
-      <c r="U54" s="15">
+        <v>2244</v>
+      </c>
+      <c r="U63" s="14">
         <f t="shared" si="25"/>
-        <v>3280.2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A55" s="8">
+        <v>2356.1999999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A64" s="8">
         <f t="shared" si="24"/>
         <v>30</v>
       </c>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15">
-        <f>$A$55*E41*$L$2*$L$3/100</f>
-        <v>937.2</v>
-      </c>
-      <c r="F55" s="15">
-        <f t="shared" ref="F55:U55" si="26">$A$55*F41*$L$2*$L$3/100</f>
-        <v>1124.6400000000001</v>
-      </c>
-      <c r="G55" s="15">
+      <c r="D64" s="14"/>
+      <c r="E64" s="14">
+        <f>$A$64*E50*$L$2*$L$3/100</f>
+        <v>673.2</v>
+      </c>
+      <c r="F64" s="14">
+        <f t="shared" ref="F64:U64" si="26">$A$64*F50*$L$2*$L$3/100</f>
+        <v>807.84000000000015</v>
+      </c>
+      <c r="G64" s="14">
         <f t="shared" si="26"/>
-        <v>1312.0800000000004</v>
-      </c>
-      <c r="H55" s="15">
+        <v>942.48000000000013</v>
+      </c>
+      <c r="H64" s="14">
         <f t="shared" si="26"/>
-        <v>1499.52</v>
-      </c>
-      <c r="I55" s="15">
+        <v>1077.1199999999999</v>
+      </c>
+      <c r="I64" s="14">
         <f t="shared" si="26"/>
-        <v>1686.96</v>
-      </c>
-      <c r="J55" s="15">
+        <v>1211.76</v>
+      </c>
+      <c r="J64" s="14">
         <f t="shared" si="26"/>
-        <v>1874.4</v>
-      </c>
-      <c r="K55" s="15">
+        <v>1346.4</v>
+      </c>
+      <c r="K64" s="14">
         <f t="shared" si="26"/>
-        <v>2249.2800000000002</v>
-      </c>
-      <c r="L55" s="15">
+        <v>1615.6800000000003</v>
+      </c>
+      <c r="L64" s="14">
         <f t="shared" si="26"/>
-        <v>2624.1600000000008</v>
-      </c>
-      <c r="M55" s="15">
+        <v>1884.9600000000003</v>
+      </c>
+      <c r="M64" s="14">
         <f t="shared" si="26"/>
-        <v>2624.1600000000008</v>
-      </c>
-      <c r="N55" s="15">
+        <v>1884.9600000000003</v>
+      </c>
+      <c r="N64" s="14">
         <f t="shared" si="26"/>
-        <v>2624.1600000000008</v>
-      </c>
-      <c r="O55" s="15">
+        <v>1884.9600000000003</v>
+      </c>
+      <c r="O64" s="14">
         <f t="shared" si="26"/>
-        <v>3186.48</v>
-      </c>
-      <c r="P55" s="15">
+        <v>2288.88</v>
+      </c>
+      <c r="P64" s="14">
         <f t="shared" si="26"/>
-        <v>3186.48</v>
-      </c>
-      <c r="Q55" s="22">
+        <v>2288.88</v>
+      </c>
+      <c r="Q64" s="21">
         <f t="shared" si="26"/>
-        <v>3373.92</v>
-      </c>
-      <c r="R55" s="15">
+        <v>2423.52</v>
+      </c>
+      <c r="R64" s="14">
         <f t="shared" si="26"/>
-        <v>3373.92</v>
-      </c>
-      <c r="S55" s="15">
+        <v>2423.52</v>
+      </c>
+      <c r="S64" s="14">
         <f t="shared" si="26"/>
-        <v>3748.8</v>
-      </c>
-      <c r="T55" s="15">
+        <v>2692.8</v>
+      </c>
+      <c r="T64" s="14">
         <f t="shared" si="26"/>
-        <v>4123.68</v>
-      </c>
-      <c r="U55" s="15">
+        <v>2962.0800000000004</v>
+      </c>
+      <c r="U64" s="14">
         <f t="shared" si="26"/>
-        <v>4311.1200000000008</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A56" s="8">
+        <v>3096.7200000000007</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A65" s="8">
         <f t="shared" si="24"/>
         <v>35</v>
       </c>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15">
-        <f>$A$56*E42*$L$2*$L$3/100</f>
-        <v>1093.4000000000001</v>
-      </c>
-      <c r="F56" s="15">
-        <f t="shared" ref="F56:U56" si="27">$A$56*F42*$L$2*$L$3/100</f>
-        <v>1530.76</v>
-      </c>
-      <c r="G56" s="15">
+      <c r="D65" s="14"/>
+      <c r="E65" s="14">
+        <f>$A$65*E51*$L$2*$L$3/100</f>
+        <v>785.40000000000009</v>
+      </c>
+      <c r="F65" s="14">
+        <f t="shared" ref="F65:U65" si="27">$A$65*F51*$L$2*$L$3/100</f>
+        <v>1099.56</v>
+      </c>
+      <c r="G65" s="14">
         <f t="shared" si="27"/>
-        <v>1530.76</v>
-      </c>
-      <c r="H56" s="15">
+        <v>1099.56</v>
+      </c>
+      <c r="H65" s="14">
         <f t="shared" si="27"/>
-        <v>1968.12</v>
-      </c>
-      <c r="I56" s="15">
+        <v>1413.72</v>
+      </c>
+      <c r="I65" s="14">
         <f t="shared" si="27"/>
-        <v>2186.8000000000002</v>
-      </c>
-      <c r="J56" s="15">
+        <v>1570.8000000000002</v>
+      </c>
+      <c r="J65" s="14">
         <f t="shared" si="27"/>
-        <v>2405.4800000000005</v>
-      </c>
-      <c r="K56" s="15">
+        <v>1727.8800000000003</v>
+      </c>
+      <c r="K65" s="14">
         <f t="shared" si="27"/>
-        <v>2842.8400000000006</v>
-      </c>
-      <c r="L56" s="15">
+        <v>2042.0400000000002</v>
+      </c>
+      <c r="L65" s="14">
         <f t="shared" si="27"/>
-        <v>3061.52</v>
-      </c>
-      <c r="M56" s="15">
+        <v>2199.12</v>
+      </c>
+      <c r="M65" s="14">
         <f t="shared" si="27"/>
-        <v>3280.2</v>
-      </c>
-      <c r="N56" s="15">
+        <v>2356.1999999999998</v>
+      </c>
+      <c r="N65" s="14">
         <f t="shared" si="27"/>
-        <v>3280.2</v>
-      </c>
-      <c r="O56" s="15">
+        <v>2356.1999999999998</v>
+      </c>
+      <c r="O65" s="14">
         <f t="shared" si="27"/>
-        <v>3936.24</v>
-      </c>
-      <c r="P56" s="15">
+        <v>2827.44</v>
+      </c>
+      <c r="P65" s="14">
         <f t="shared" si="27"/>
-        <v>4154.920000000001</v>
-      </c>
-      <c r="Q56" s="22">
+        <v>2984.5200000000004</v>
+      </c>
+      <c r="Q65" s="21">
         <f t="shared" si="27"/>
-        <v>4373.6000000000004</v>
-      </c>
-      <c r="R56" s="15">
+        <v>3141.6000000000004</v>
+      </c>
+      <c r="R65" s="14">
         <f t="shared" si="27"/>
-        <v>4373.6000000000004</v>
-      </c>
-      <c r="S56" s="15">
+        <v>3141.6000000000004</v>
+      </c>
+      <c r="S65" s="14">
         <f t="shared" si="27"/>
-        <v>4592.2800000000007</v>
-      </c>
-      <c r="T56" s="15">
+        <v>3298.6800000000007</v>
+      </c>
+      <c r="T65" s="14">
         <f t="shared" si="27"/>
-        <v>5029.6400000000003</v>
-      </c>
-      <c r="U56" s="15">
+        <v>3612.8400000000006</v>
+      </c>
+      <c r="U65" s="14">
         <f t="shared" si="27"/>
-        <v>5467.0000000000009</v>
-      </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="D61" t="s">
-        <v>48</v>
-      </c>
-      <c r="F61" s="11">
-        <f>F62/2-SQRT((F62/2)*(F62/2)-F63*F63)</f>
-        <v>135.42486889354092</v>
-      </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="D62" t="s">
-        <v>45</v>
-      </c>
-      <c r="F62" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="D63" t="s">
-        <v>46</v>
-      </c>
-      <c r="F63" s="9">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="F67" s="8" t="s">
+        <v>3927.0000000000005</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="F76" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H76" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G67" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H67" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="E68" t="s">
-        <v>52</v>
-      </c>
-      <c r="F68" s="24">
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="E77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F77" s="23">
         <v>4</v>
       </c>
-      <c r="G68" s="24">
+      <c r="G77" s="23">
         <f>2.25*2.25</f>
         <v>5.0625</v>
       </c>
-      <c r="H68" s="24">
+      <c r="H77" s="23">
         <f>2.5*2.5</f>
         <v>6.25</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B69" t="s">
-        <v>54</v>
-      </c>
-      <c r="E69" t="s">
-        <v>49</v>
-      </c>
-      <c r="F69" s="4">
-        <f>Q46+$H$2</f>
-        <v>2660</v>
-      </c>
-      <c r="G69" s="15">
-        <f>S46+$H$2</f>
-        <v>3200</v>
-      </c>
-      <c r="H69" s="4">
-        <f>U46+$H$2</f>
-        <v>3800</v>
-      </c>
-      <c r="J69" s="4"/>
-      <c r="K69" s="15"/>
-      <c r="L69" s="4"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B70" t="s">
-        <v>56</v>
-      </c>
-      <c r="E70" t="s">
-        <v>50</v>
-      </c>
-      <c r="F70" s="4">
-        <f t="shared" ref="F70:F71" si="28">Q47+$H$2</f>
-        <v>3350</v>
-      </c>
-      <c r="G70" s="15">
-        <f>S47+$H$2</f>
-        <v>4043.75</v>
-      </c>
-      <c r="H70" s="4">
-        <f t="shared" ref="H70:H71" si="29">U47+$H$2</f>
-        <v>4812.5</v>
-      </c>
-      <c r="J70" s="4"/>
-      <c r="K70" s="15"/>
-      <c r="L70" s="4"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="E71" t="s">
-        <v>51</v>
-      </c>
-      <c r="F71" s="4">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>42</v>
+      </c>
+      <c r="E78" t="s">
+        <v>37</v>
+      </c>
+      <c r="F78" s="4">
+        <f>Q55+$H$2</f>
+        <v>1584</v>
+      </c>
+      <c r="G78" s="14">
+        <f>S55+$H$2</f>
+        <v>1980</v>
+      </c>
+      <c r="H78" s="4">
+        <f>U55+$H$2</f>
+        <v>2420</v>
+      </c>
+      <c r="J78" s="4"/>
+      <c r="K78" s="14"/>
+      <c r="L78" s="4"/>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>44</v>
+      </c>
+      <c r="E79" t="s">
+        <v>38</v>
+      </c>
+      <c r="F79" s="4">
+        <f t="shared" ref="F79:F80" si="28">Q56+$H$2</f>
+        <v>2090.0000000000005</v>
+      </c>
+      <c r="G79" s="14">
+        <f>S56+$H$2</f>
+        <v>2598.7500000000005</v>
+      </c>
+      <c r="H79" s="4">
+        <f t="shared" ref="H79:H80" si="29">U56+$H$2</f>
+        <v>3162.5000000000005</v>
+      </c>
+      <c r="J79" s="4"/>
+      <c r="K79" s="14"/>
+      <c r="L79" s="4"/>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="E80" t="s">
+        <v>39</v>
+      </c>
+      <c r="F80" s="4">
         <f t="shared" si="28"/>
-        <v>4100</v>
-      </c>
-      <c r="G71" s="15">
-        <f>S48+$H$2</f>
-        <v>4955</v>
-      </c>
-      <c r="H71" s="4">
+        <v>2640</v>
+      </c>
+      <c r="G80" s="14">
+        <f>S57+$H$2</f>
+        <v>3267</v>
+      </c>
+      <c r="H80" s="4">
         <f t="shared" si="29"/>
-        <v>6125</v>
-      </c>
-      <c r="J71" s="4"/>
-      <c r="K71" s="15"/>
-      <c r="L71" s="4"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="E73" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="E74" t="s">
-        <v>49</v>
-      </c>
-      <c r="F74" s="8">
-        <f>Q10</f>
+        <v>4125</v>
+      </c>
+      <c r="J80" s="4"/>
+      <c r="K80" s="14"/>
+      <c r="L80" s="4"/>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E82" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E83" t="s">
+        <v>37</v>
+      </c>
+      <c r="F83" s="8">
+        <f>Q19</f>
         <v>2080</v>
       </c>
-      <c r="G74" s="23">
-        <f>S10</f>
+      <c r="G83" s="22">
+        <f>S19</f>
         <v>2632.5</v>
       </c>
-      <c r="H74" s="23">
-        <f>U10</f>
+      <c r="H83" s="22">
+        <f>U19</f>
         <v>3250</v>
       </c>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="E75" t="s">
-        <v>50</v>
-      </c>
-      <c r="F75" s="8">
-        <f t="shared" ref="F75:F76" si="30">Q11</f>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E84" t="s">
+        <v>38</v>
+      </c>
+      <c r="F84" s="8">
+        <f t="shared" ref="F84:F85" si="30">Q20</f>
         <v>2600</v>
       </c>
-      <c r="G75" s="23">
-        <f t="shared" ref="G75:G76" si="31">S11</f>
+      <c r="G84" s="22">
+        <f t="shared" ref="G84:G85" si="31">S20</f>
         <v>3290.625</v>
       </c>
-      <c r="H75" s="23">
-        <f t="shared" ref="H75:H76" si="32">U11</f>
+      <c r="H84" s="22">
+        <f t="shared" ref="H84:H85" si="32">U20</f>
         <v>4062.5</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="E76" t="s">
-        <v>51</v>
-      </c>
-      <c r="F76" s="8">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="E85" t="s">
+        <v>39</v>
+      </c>
+      <c r="F85" s="8">
         <f t="shared" si="30"/>
         <v>3120</v>
       </c>
-      <c r="G76" s="23">
+      <c r="G85" s="22">
         <f t="shared" si="31"/>
         <v>3948.75</v>
       </c>
-      <c r="H76" s="23">
+      <c r="H85" s="22">
         <f t="shared" si="32"/>
         <v>4875</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="D78" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B80" t="s">
-        <v>59</v>
-      </c>
-      <c r="G80" s="17">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>47</v>
+      </c>
+      <c r="G89" s="16">
         <v>250</v>
       </c>
     </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B81" t="s">
-        <v>58</v>
-      </c>
-      <c r="G81" s="17">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>46</v>
+      </c>
+      <c r="G90" s="16">
         <f>8*35*P2</f>
-        <v>840</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B82" t="s">
-        <v>57</v>
-      </c>
-      <c r="E82" s="4"/>
-      <c r="G82" s="4">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>45</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="G91" s="4">
         <f>(120*4+260*5)*0.2*P2</f>
-        <v>1068</v>
+        <v>783.2</v>
       </c>
     </row>
   </sheetData>
